--- a/ROSALES/Diciembre/expensas rosales Diciembre.xlsx
+++ b/ROSALES/Diciembre/expensas rosales Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15073B31-9AF9-45A3-B887-C52FE81C0C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9A7BE8-978E-49F6-BA85-448C78A78EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$67</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="126">
   <si>
     <t>TOTAL</t>
   </si>
@@ -361,9 +361,6 @@
 Les recordamos que el pago debe realizarse con dinero justo.</t>
   </si>
   <si>
-    <t>PREVISION EXTRAORDINARIA</t>
-  </si>
-  <si>
     <t>LAS LINEAS GRISES CORRESPONDEN A PLANES DE PAGO VIGENTES -  RESTA ABONAR 6 CUOTAS DE $107.386,20 + LAS EXPENSAS AL DIA - PARTE DE LA DEUDA CANCELA EDESUR Y EXPENSAS CON TASA DE INTERES MENSUAL</t>
   </si>
   <si>
@@ -382,15 +379,6 @@
     <t>PUNITORIOS MAL COBRADOS</t>
   </si>
   <si>
-    <t xml:space="preserve">Cuota 1 revaluo ARBA </t>
-  </si>
-  <si>
-    <t>Sr. Leonardo Balcazza - Mano de obra y materiales - Arreglo medianera</t>
-  </si>
-  <si>
-    <t>CUOTA PLAN DE PAGOS (4/6)</t>
-  </si>
-  <si>
     <t>EDESUR</t>
   </si>
   <si>
@@ -407,6 +395,18 @@
   </si>
   <si>
     <t>TSG MES 11</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Cerrajeria Aryam - Copia de llaves</t>
+  </si>
+  <si>
+    <t>PREVISION EXTRAORDINARIA - ARBA - ULTIMA CUOTA PERIODO 2025</t>
+  </si>
+  <si>
+    <t>CUOTA PLAN DE PAGOS (5/6)</t>
   </si>
 </sst>
 </file>
@@ -428,7 +428,7 @@
     <numFmt numFmtId="173" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="174" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -652,6 +652,14 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="14">
@@ -1031,7 +1039,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1324,7 +1332,6 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="26" fillId="11" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="25" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1355,26 +1362,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="26" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1416,9 +1415,11 @@
     <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1508,11 +1509,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>649605</xdr:colOff>
+      <xdr:colOff>249555</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>28576</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2009775" cy="739139"/>
+    <xdr:ext cx="2274570" cy="914400"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="image1.jpg">
@@ -1532,8 +1533,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1685925" y="381000"/>
-          <a:ext cx="2009775" cy="739139"/>
+          <a:off x="1259205" y="295276"/>
+          <a:ext cx="2274570" cy="914400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1836,17 +1837,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F65"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:F68"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1854,143 +1855,143 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>105</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="238">
+      <c r="C18" s="213">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="221">
-        <v>316973.44</v>
+      <c r="C19" s="215">
+        <v>330057.21999999997</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="238">
+      <c r="C20" s="213">
         <v>85000</v>
       </c>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="238">
+      <c r="C21" s="213">
         <v>15748</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6"/>
       <c r="F21" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="220">
+      <c r="C22" s="213">
         <v>83400</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="40"/>
       <c r="B23" s="41"/>
-      <c r="C23" s="222">
+      <c r="C23" s="212">
         <f>SUM(C17:C22)</f>
-        <v>577775.43999999994</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+        <v>590859.22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
         <v>12</v>
       </c>
@@ -1999,317 +2000,341 @@
       <c r="D24" s="45"/>
       <c r="F24" s="12"/>
     </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
         <v>97</v>
       </c>
       <c r="B25" s="42"/>
-      <c r="C25" s="220">
+      <c r="C25" s="213">
         <f>349151.87+ (349151.87*10%)</f>
         <v>384067.05699999997</v>
       </c>
       <c r="D25" s="45"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="B26" s="42"/>
-      <c r="C26" s="220">
-        <v>5684</v>
+      <c r="C26" s="213">
+        <v>192033.53</v>
       </c>
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="B27" s="42"/>
-      <c r="C27" s="238">
+      <c r="C27" s="213">
+        <v>5684</v>
+      </c>
+      <c r="D27" s="45"/>
+      <c r="F27" s="12"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" s="42"/>
+      <c r="C28" s="213">
+        <v>10000</v>
+      </c>
+      <c r="D28" s="45"/>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="42"/>
+      <c r="C29" s="213">
         <v>55000</v>
       </c>
-      <c r="F27" s="12"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="28" t="s">
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="39"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="12"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="40"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="23">
-        <f>SUM(C24:C28)</f>
-        <v>444751.05699999997</v>
-      </c>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="30" t="s">
+      <c r="B30" s="39"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="40"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="23">
+        <f>SUM(C24:C30)</f>
+        <v>646784.58699999994</v>
+      </c>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="43">
-        <f>+C29+C23</f>
-        <v>1022526.497</v>
-      </c>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C31" s="24"/>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="13" t="s">
+      <c r="B32" s="30"/>
+      <c r="C32" s="43">
+        <f>+C31+C23</f>
+        <v>1237643.807</v>
+      </c>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C33" s="24"/>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="24"/>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="220">
-        <v>610000</v>
-      </c>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="240">
-        <v>1034026.5</v>
-      </c>
+      <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="28"/>
       <c r="B35" s="28"/>
-      <c r="C35" s="34"/>
+      <c r="C35" s="211"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C36" s="25"/>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="211"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="173" t="s">
-        <v>110</v>
-      </c>
-      <c r="B37" s="173"/>
-      <c r="C37" s="174">
-        <v>0</v>
-      </c>
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="34"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C38" s="25"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="13" t="s">
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="173" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" s="173"/>
+      <c r="C39" s="174">
+        <v>1000000</v>
+      </c>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C40" s="25"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="14">
-        <f>+C33+C34+C35+C38</f>
-        <v>1644026.5</v>
-      </c>
-      <c r="E39" s="6"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="18" t="s">
+      <c r="B41" s="13"/>
+      <c r="C41" s="14">
+        <f>+C35+C36+C37+C40</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="19">
-        <f>+C39+C30</f>
-        <v>2666552.997</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="227" t="s">
+      <c r="B43" s="18"/>
+      <c r="C43" s="19">
+        <f>+C41+C32</f>
+        <v>1237643.807</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="220" t="s">
         <v>109</v>
       </c>
-      <c r="B43" s="228"/>
-      <c r="C43" s="228"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="228"/>
-      <c r="B44" s="228"/>
-      <c r="C44" s="228"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="228"/>
-      <c r="B45" s="228"/>
-      <c r="C45" s="228"/>
-    </row>
-    <row r="46" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="228"/>
-      <c r="B46" s="228"/>
-      <c r="C46" s="228"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-    </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
-      <c r="C47" s="154"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="201" t="s">
-        <v>100</v>
-      </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="202">
-        <v>1081522.6958899994</v>
-      </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="201" t="s">
-        <v>124</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="31">
-        <f>-(C41-C28)</f>
-        <v>-2666552.997</v>
-      </c>
+      <c r="B45" s="221"/>
+      <c r="C45" s="221"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="221"/>
+      <c r="B46" s="221"/>
+      <c r="C46" s="221"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="221"/>
+      <c r="B47" s="221"/>
+      <c r="C47" s="221"/>
+    </row>
+    <row r="48" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="221"/>
+      <c r="B48" s="221"/>
+      <c r="C48" s="221"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4"/>
+      <c r="C49" s="154"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="201" t="s">
-        <v>96</v>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="200" t="s">
+        <v>100</v>
       </c>
       <c r="B50" s="28"/>
-      <c r="C50" s="203">
-        <f>'prorrateo '!F31</f>
-        <v>2610074.1626310009</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="201" t="s">
-        <v>116</v>
+      <c r="C50" s="201">
+        <v>1137430.0615210002</v>
+      </c>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="200" t="s">
+        <v>120</v>
       </c>
       <c r="B51" s="28"/>
       <c r="C51" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="201" t="s">
-        <v>119</v>
+        <f>-(C43-C30)</f>
+        <v>-1237643.807</v>
+      </c>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="200" t="s">
+        <v>96</v>
       </c>
       <c r="B52" s="28"/>
-      <c r="C52" s="203">
+      <c r="C52" s="202">
+        <f>'prorrateo '!F31</f>
+        <v>2466028.3590707099</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="200" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" s="28"/>
+      <c r="C53" s="235">
+        <f>-Edesur!C7</f>
+        <v>-666521.55000000005</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="200" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" s="28"/>
+      <c r="C54" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="200" t="s">
+        <v>125</v>
+      </c>
+      <c r="B55" s="28"/>
+      <c r="C55" s="202">
         <v>107386.2</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="201" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="200" t="s">
         <v>8</v>
       </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="202">
-        <f>SUM(C48:C52)</f>
-        <v>1132430.0615210002</v>
-      </c>
-      <c r="D53" s="5"/>
-    </row>
-    <row r="54" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="9"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="10"/>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="223"/>
-      <c r="B55" s="223"/>
-      <c r="C55" s="223"/>
-      <c r="F55" s="44"/>
-    </row>
-    <row r="56" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="224"/>
-      <c r="B56" s="224"/>
-      <c r="C56" s="224"/>
-    </row>
-    <row r="57" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="26" t="s">
+      <c r="B56" s="28"/>
+      <c r="C56" s="201">
+        <f>SUM(C50:C55)</f>
+        <v>1806679.26359171</v>
+      </c>
+      <c r="D56" s="5"/>
+    </row>
+    <row r="57" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="9"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="10"/>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="216"/>
+      <c r="B58" s="216"/>
+      <c r="C58" s="216"/>
+      <c r="F58" s="44"/>
+    </row>
+    <row r="59" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="217"/>
+      <c r="B59" s="217"/>
+      <c r="C59" s="217"/>
+    </row>
+    <row r="60" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B57" s="27"/>
-      <c r="C57" s="29"/>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="28" t="s">
+      <c r="B60" s="27"/>
+      <c r="C60" s="29"/>
+    </row>
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B58" s="28"/>
-      <c r="C58" s="31">
-        <f>-C39</f>
-        <v>-1644026.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="28"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="31"/>
-    </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="28"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="32"/>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="155" t="s">
-        <v>0</v>
-      </c>
-      <c r="B61" s="156"/>
-      <c r="C61" s="157">
-        <f>SUM(C57:C60)</f>
-        <v>-1644026.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="225" t="s">
+      <c r="B61" s="28"/>
+      <c r="C61" s="31">
+        <f>-C41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="28"/>
+      <c r="B62" s="28"/>
+      <c r="C62" s="31"/>
+    </row>
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="28"/>
+      <c r="B63" s="28"/>
+      <c r="C63" s="32"/>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="155" t="s">
+        <v>0</v>
+      </c>
+      <c r="B64" s="156"/>
+      <c r="C64" s="157">
+        <f>SUM(C60:C63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="218" t="s">
         <v>107</v>
       </c>
-      <c r="B62" s="226"/>
-      <c r="C62" s="226"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="226"/>
-      <c r="B63" s="226"/>
-      <c r="C63" s="226"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="226"/>
-      <c r="B64" s="226"/>
-      <c r="C64" s="226"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
+      <c r="B65" s="219"/>
+      <c r="C65" s="219"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="219"/>
+      <c r="B66" s="219"/>
+      <c r="C66" s="219"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="219"/>
+      <c r="B67" s="219"/>
+      <c r="C67" s="219"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A55:C56"/>
-    <mergeCell ref="A62:C64"/>
-    <mergeCell ref="A43:C46"/>
+    <mergeCell ref="A58:C59"/>
+    <mergeCell ref="A65:C67"/>
+    <mergeCell ref="A45:C48"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <hyperlinks>
@@ -2328,56 +2353,56 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="9" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="11" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="229">
+      <c r="B1" s="222">
         <f>N1</f>
-        <v>1017526.497</v>
-      </c>
-      <c r="C1" s="229"/>
+        <v>1237643.807</v>
+      </c>
+      <c r="C1" s="222"/>
       <c r="D1" s="138">
         <v>1667839.1270000001</v>
       </c>
       <c r="E1" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="231"/>
-      <c r="H1" s="231"/>
-      <c r="I1" s="232" t="s">
-        <v>114</v>
-      </c>
-      <c r="J1" s="232"/>
-      <c r="K1" s="232"/>
-      <c r="L1" s="229">
+      <c r="G1" s="224"/>
+      <c r="H1" s="224"/>
+      <c r="I1" s="225" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1" s="225"/>
+      <c r="K1" s="225"/>
+      <c r="L1" s="222">
         <v>1000000</v>
       </c>
-      <c r="M1" s="229"/>
+      <c r="M1" s="222"/>
       <c r="N1">
-        <v>1017526.497</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1237643.807</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
@@ -2399,17 +2424,17 @@
       <c r="G2" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="200" t="s">
+      <c r="H2" s="199" t="s">
         <v>92</v>
       </c>
       <c r="I2" s="50" t="s">
         <v>104</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="K2" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L2" s="50" t="s">
         <v>108</v>
@@ -2418,10 +2443,10 @@
         <v>30</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2435,11 +2460,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E3" s="129">
-        <v>105505.57938970001</v>
-      </c>
-      <c r="F3" s="217">
+        <v>134104.34113548099</v>
+      </c>
+      <c r="F3" s="232">
         <f>E3</f>
-        <v>105505.57938970001</v>
+        <v>134104.34113548099</v>
       </c>
       <c r="G3" s="56">
         <f>E3-F3</f>
@@ -2451,11 +2476,11 @@
       </c>
       <c r="I3" s="56">
         <f>B$1*D3/100</f>
-        <v>51995.603996700003</v>
+        <v>63243.598537700011</v>
       </c>
       <c r="J3" s="56">
         <f>Edesur!N10</f>
-        <v>36867.389952781006</v>
+        <v>38657.764744019987</v>
       </c>
       <c r="K3" s="56">
         <f>G$1*D3/100</f>
@@ -2467,15 +2492,15 @@
       </c>
       <c r="M3" s="57">
         <f>I3+G3+L3+K3+H3+J3</f>
-        <v>139962.993949481</v>
+        <v>153001.36328172</v>
       </c>
       <c r="N3" s="44"/>
       <c r="O3" s="151">
         <f>M3-J3</f>
-        <v>103095.6039967</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+        <v>114343.59853770002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2489,11 +2514,11 @@
         <v>5.09</v>
       </c>
       <c r="E4" s="129">
-        <v>104519.0115643</v>
-      </c>
-      <c r="F4" s="217">
+        <v>130106.86867093903</v>
+      </c>
+      <c r="F4" s="232">
         <f>E4</f>
-        <v>104519.0115643</v>
+        <v>130106.86867093903</v>
       </c>
       <c r="G4" s="56">
         <f t="shared" ref="G4:G29" si="0">E4-F4</f>
@@ -2505,11 +2530,11 @@
       </c>
       <c r="I4" s="56">
         <f t="shared" ref="I4:I29" si="2">B$1*D4/100</f>
-        <v>51792.098697299996</v>
+        <v>62996.069776299999</v>
       </c>
       <c r="J4" s="56">
         <f>Edesur!N11</f>
-        <v>33250.492639639029</v>
+        <v>34271.621392379988</v>
       </c>
       <c r="K4" s="56">
         <f t="shared" ref="K4:K29" si="3">G$1*D4/100</f>
@@ -2521,15 +2546,15 @@
       </c>
       <c r="M4" s="57">
         <f t="shared" ref="M4:M29" si="5">I4+G4+L4+K4+H4+J4</f>
-        <v>135942.59133693902</v>
+        <v>148167.69116867997</v>
       </c>
       <c r="N4" s="44"/>
       <c r="O4" s="151">
         <f t="shared" ref="O4:O29" si="6">M4-J4</f>
-        <v>102692.09869729998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>113896.06977629999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2541,27 +2566,27 @@
         <v>5.04</v>
       </c>
       <c r="E5" s="129">
-        <v>407656.00631120004</v>
-      </c>
-      <c r="F5" s="217">
-        <f>497170.55-64957-F23</f>
-        <v>377751.01123959996</v>
+        <v>160726.72885904807</v>
+      </c>
+      <c r="F5" s="232">
+        <f>160000-F23</f>
+        <v>134409.67677473198</v>
       </c>
       <c r="G5" s="56">
         <f t="shared" si="0"/>
-        <v>29904.995071600075</v>
+        <v>26317.052084316092</v>
       </c>
       <c r="H5" s="56">
         <f t="shared" si="1"/>
-        <v>1196.199802864003</v>
+        <v>1052.6820833726438</v>
       </c>
       <c r="I5" s="56">
         <f t="shared" si="2"/>
-        <v>51283.335448799997</v>
+        <v>62377.247872799999</v>
       </c>
       <c r="J5" s="56">
         <f>Edesur!N12</f>
-        <v>33720.595831784012</v>
+        <v>47606.474713279997</v>
       </c>
       <c r="K5" s="56">
         <f t="shared" si="3"/>
@@ -2573,64 +2598,67 @@
       </c>
       <c r="M5" s="57">
         <f t="shared" si="5"/>
-        <v>166505.12615504808</v>
+        <v>187753.45675376873</v>
       </c>
       <c r="N5" s="44"/>
       <c r="O5" s="151">
         <f t="shared" si="6"/>
-        <v>132784.53032326407</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="139" t="s">
+        <v>140146.98204048874</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="140"/>
-      <c r="C6" s="141" t="s">
+      <c r="B6" s="198"/>
+      <c r="C6" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="142">
+      <c r="D6" s="176">
         <v>5.21</v>
       </c>
-      <c r="E6" s="143">
-        <v>107734.41851670001</v>
-      </c>
-      <c r="F6" s="219"/>
-      <c r="G6" s="144">
+      <c r="E6" s="129">
+        <v>242855.68957555902</v>
+      </c>
+      <c r="F6" s="232">
+        <f>E6</f>
+        <v>242855.68957555902</v>
+      </c>
+      <c r="G6" s="64">
         <f t="shared" si="0"/>
-        <v>107734.41851670001</v>
-      </c>
-      <c r="H6" s="144">
+        <v>0</v>
+      </c>
+      <c r="H6" s="64">
         <f t="shared" si="1"/>
-        <v>4309.3767406680008</v>
-      </c>
-      <c r="I6" s="144">
+        <v>0</v>
+      </c>
+      <c r="I6" s="64">
         <f t="shared" si="2"/>
-        <v>53013.130493700002</v>
-      </c>
-      <c r="J6" s="144">
+        <v>64481.242344700004</v>
+      </c>
+      <c r="J6" s="64">
         <f>Edesur!N13</f>
-        <v>31672.067378491014</v>
-      </c>
-      <c r="K6" s="144">
+        <v>34675.13340222001</v>
+      </c>
+      <c r="K6" s="64">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L6" s="144">
+      <c r="L6" s="64">
         <f t="shared" si="4"/>
         <v>52100</v>
       </c>
-      <c r="M6" s="145">
+      <c r="M6" s="231">
         <f t="shared" si="5"/>
-        <v>248828.99312955904</v>
+        <v>151256.37574692001</v>
       </c>
       <c r="O6" s="151">
         <f t="shared" si="6"/>
-        <v>217156.92575106802</v>
+        <v>116581.2423447</v>
       </c>
       <c r="P6" s="175"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
@@ -2644,11 +2672,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E7" s="129">
-        <v>105666.57938970001</v>
-      </c>
-      <c r="F7" s="217">
+        <v>130486.97654548101</v>
+      </c>
+      <c r="F7" s="232">
         <f t="shared" ref="F7:F11" si="7">E7</f>
-        <v>105666.57938970001</v>
+        <v>130486.97654548101</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" si="0"/>
@@ -2660,11 +2688,11 @@
       </c>
       <c r="I7" s="56">
         <f t="shared" si="2"/>
-        <v>51995.603996700003</v>
+        <v>63243.598537700011</v>
       </c>
       <c r="J7" s="56">
         <f>Edesur!N14</f>
-        <v>33250.025362781016</v>
+        <v>38610.871244020003</v>
       </c>
       <c r="K7" s="56">
         <f t="shared" si="3"/>
@@ -2676,15 +2704,15 @@
       </c>
       <c r="M7" s="57">
         <f t="shared" si="5"/>
-        <v>136345.62935948101</v>
+        <v>152954.46978172002</v>
       </c>
       <c r="O7" s="151">
         <f t="shared" si="6"/>
-        <v>103095.6039967</v>
+        <v>114343.59853770002</v>
       </c>
       <c r="P7" s="175"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
         <v>40</v>
       </c>
@@ -2696,11 +2724,11 @@
         <v>5.09</v>
       </c>
       <c r="E8" s="129">
-        <v>105253.0115643</v>
-      </c>
-      <c r="F8" s="217">
+        <v>128193.61387093902</v>
+      </c>
+      <c r="F8" s="232">
         <f t="shared" si="7"/>
-        <v>105253.0115643</v>
+        <v>128193.61387093902</v>
       </c>
       <c r="G8" s="56">
         <f t="shared" si="0"/>
@@ -2712,11 +2740,11 @@
       </c>
       <c r="I8" s="56">
         <f t="shared" si="2"/>
-        <v>51792.098697299996</v>
+        <v>62996.069776299999</v>
       </c>
       <c r="J8" s="56">
         <f>Edesur!N15</f>
-        <v>31337.237839639023</v>
+        <v>39683.131292380014</v>
       </c>
       <c r="K8" s="56">
         <f t="shared" si="3"/>
@@ -2728,14 +2756,14 @@
       </c>
       <c r="M8" s="57">
         <f t="shared" si="5"/>
-        <v>134029.33653693902</v>
+        <v>153579.20106868001</v>
       </c>
       <c r="O8" s="151">
         <f t="shared" si="6"/>
-        <v>102692.0986973</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>113896.06977629999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>42</v>
       </c>
@@ -2747,15 +2775,15 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E9" s="129">
-        <v>105666.57938970001</v>
-      </c>
-      <c r="F9" s="217">
-        <f t="shared" si="7"/>
-        <v>105666.57938970001</v>
+        <v>129633.514845481</v>
+      </c>
+      <c r="F9" s="232">
+        <f>130000</f>
+        <v>130000</v>
       </c>
       <c r="G9" s="56">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-366.48515451900312</v>
       </c>
       <c r="H9" s="56">
         <f t="shared" si="1"/>
@@ -2763,11 +2791,11 @@
       </c>
       <c r="I9" s="56">
         <f t="shared" si="2"/>
-        <v>51995.603996700003</v>
+        <v>63243.598537700011</v>
       </c>
       <c r="J9" s="56">
         <f>Edesur!N16</f>
-        <v>32396.563662781002</v>
+        <v>31220.45564402001</v>
       </c>
       <c r="K9" s="56">
         <f t="shared" si="3"/>
@@ -2779,15 +2807,15 @@
       </c>
       <c r="M9" s="57">
         <f t="shared" si="5"/>
-        <v>135492.167659481</v>
+        <v>145197.56902720104</v>
       </c>
       <c r="O9" s="151">
         <f t="shared" si="6"/>
-        <v>103095.6039967</v>
+        <v>113977.11338318103</v>
       </c>
       <c r="P9" s="175"/>
     </row>
-    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="177" t="s">
         <v>44</v>
       </c>
@@ -2801,11 +2829,11 @@
         <v>5.09</v>
       </c>
       <c r="E10" s="181">
-        <v>105253.0115643</v>
-      </c>
-      <c r="F10" s="218">
+        <v>122885.26967093899</v>
+      </c>
+      <c r="F10" s="233">
         <f t="shared" si="7"/>
-        <v>105253.0115643</v>
+        <v>122885.26967093899</v>
       </c>
       <c r="G10" s="182">
         <f t="shared" si="0"/>
@@ -2814,11 +2842,11 @@
       <c r="H10" s="182"/>
       <c r="I10" s="182">
         <f t="shared" si="2"/>
-        <v>51792.098697299996</v>
+        <v>62996.069776299999</v>
       </c>
       <c r="J10" s="182">
         <f>Edesur!N17</f>
-        <v>26028.893639638987</v>
+        <v>21132.062692379994</v>
       </c>
       <c r="K10" s="182">
         <f t="shared" si="3"/>
@@ -2830,14 +2858,14 @@
       </c>
       <c r="M10" s="183">
         <f t="shared" si="5"/>
-        <v>128720.99233693899</v>
+        <v>135028.13246867998</v>
       </c>
       <c r="O10" s="151">
         <f t="shared" si="6"/>
-        <v>102692.0986973</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>113896.06977629999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -2849,11 +2877,11 @@
         <v>5.04</v>
       </c>
       <c r="E11" s="129">
-        <v>104219.09200080001</v>
-      </c>
-      <c r="F11" s="217">
+        <v>127318.37378458401</v>
+      </c>
+      <c r="F11" s="232">
         <f t="shared" si="7"/>
-        <v>104219.09200080001</v>
+        <v>127318.37378458401</v>
       </c>
       <c r="G11" s="56">
         <f t="shared" si="0"/>
@@ -2865,11 +2893,11 @@
       </c>
       <c r="I11" s="56">
         <f t="shared" si="2"/>
-        <v>51283.335448799997</v>
+        <v>62377.247872799999</v>
       </c>
       <c r="J11" s="56">
         <f>Edesur!N18</f>
-        <v>31413.435631783999</v>
+        <v>30359.045413280011</v>
       </c>
       <c r="K11" s="56">
         <f t="shared" si="3"/>
@@ -2881,14 +2909,14 @@
       </c>
       <c r="M11" s="57">
         <f t="shared" si="5"/>
-        <v>133096.771080584</v>
+        <v>143136.29328608001</v>
       </c>
       <c r="O11" s="151">
         <f t="shared" si="6"/>
-        <v>101683.3354488</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+        <v>112777.2478728</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
         <v>47</v>
       </c>
@@ -2900,11 +2928,11 @@
         <v>5.21</v>
       </c>
       <c r="E12" s="129">
-        <v>107734.41851670001</v>
-      </c>
-      <c r="F12" s="217">
+        <v>144392.25191819097</v>
+      </c>
+      <c r="F12" s="232">
         <f t="shared" ref="F12" si="8">E12</f>
-        <v>107734.41851670001</v>
+        <v>144392.25191819097</v>
       </c>
       <c r="G12" s="56">
         <f t="shared" si="0"/>
@@ -2916,11 +2944,11 @@
       </c>
       <c r="I12" s="56">
         <f t="shared" si="2"/>
-        <v>53013.130493700002</v>
+        <v>64481.242344700004</v>
       </c>
       <c r="J12" s="56">
         <f>Edesur!N19</f>
-        <v>45252.424978490948</v>
+        <v>50525.136402220058</v>
       </c>
       <c r="K12" s="56">
         <f t="shared" si="3"/>
@@ -2932,14 +2960,14 @@
       </c>
       <c r="M12" s="57">
         <f t="shared" si="5"/>
-        <v>150365.55547219096</v>
+        <v>167106.37874692006</v>
       </c>
       <c r="O12" s="151">
         <f t="shared" si="6"/>
-        <v>105113.13049370001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+        <v>116581.2423447</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>49</v>
       </c>
@@ -2953,11 +2981,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E13" s="129">
-        <v>105666.57938970001</v>
-      </c>
-      <c r="F13" s="217">
+        <v>175045.18024548097</v>
+      </c>
+      <c r="F13" s="232">
         <f>E13</f>
-        <v>105666.57938970001</v>
+        <v>175045.18024548097</v>
       </c>
       <c r="G13" s="56">
         <f t="shared" si="0"/>
@@ -2969,11 +2997,11 @@
       </c>
       <c r="I13" s="56">
         <f t="shared" si="2"/>
-        <v>51995.603996700003</v>
+        <v>63243.598537700011</v>
       </c>
       <c r="J13" s="56">
         <f>Edesur!N20</f>
-        <v>77808.229062780985</v>
+        <v>47858.269444020021</v>
       </c>
       <c r="K13" s="56">
         <f t="shared" si="3"/>
@@ -2985,19 +3013,19 @@
       </c>
       <c r="M13" s="57">
         <f t="shared" si="5"/>
-        <v>180903.833059481</v>
+        <v>162201.86798172005</v>
       </c>
       <c r="N13" s="44"/>
       <c r="O13" s="151">
         <f t="shared" si="6"/>
-        <v>103095.60399670001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>114343.59853770002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="199" t="s">
+      <c r="B14" s="198" t="s">
         <v>106</v>
       </c>
       <c r="C14" s="63" t="s">
@@ -3007,15 +3035,15 @@
         <v>5.09</v>
       </c>
       <c r="E14" s="129">
-        <v>371509.96055870003</v>
-      </c>
-      <c r="F14" s="217">
-        <f>580000-F25-84879</f>
-        <v>416293.74475960003</v>
+        <v>83972.551670038971</v>
+      </c>
+      <c r="F14" s="232">
+        <f>109600-F25</f>
+        <v>84009.676774731997</v>
       </c>
       <c r="G14" s="64">
         <f t="shared" si="0"/>
-        <v>-44783.784200900001</v>
+        <v>-37.125104693026515</v>
       </c>
       <c r="H14" s="64">
         <f t="shared" si="1"/>
@@ -3023,11 +3051,11 @@
       </c>
       <c r="I14" s="64">
         <f t="shared" si="2"/>
-        <v>51792.098697299996</v>
+        <v>62996.069776299999</v>
       </c>
       <c r="J14" s="56">
         <f>Edesur!N21</f>
-        <v>31899.959839638981</v>
+        <v>25136.76759238002</v>
       </c>
       <c r="K14" s="64">
         <f t="shared" si="3"/>
@@ -3039,14 +3067,14 @@
       </c>
       <c r="M14" s="57">
         <f t="shared" si="5"/>
-        <v>89808.274336038972</v>
+        <v>138995.71226398699</v>
       </c>
       <c r="O14" s="151">
         <f t="shared" si="6"/>
-        <v>57908.314496399995</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>113858.94467160697</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>53</v>
       </c>
@@ -3060,27 +3088,24 @@
         <v>5.04</v>
       </c>
       <c r="E15" s="129">
-        <v>104219.09188079997</v>
-      </c>
-      <c r="F15" s="217">
-        <f>104219-F29+22333.1-0.35</f>
-        <v>104219.0874284</v>
-      </c>
+        <v>124636.07021507998</v>
+      </c>
+      <c r="F15" s="232"/>
       <c r="G15" s="56">
         <f t="shared" si="0"/>
-        <v>4.4523999677039683E-3</v>
+        <v>124636.07021507998</v>
       </c>
       <c r="H15" s="56">
         <f t="shared" si="1"/>
-        <v>1.7809599870815873E-4</v>
+        <v>4985.4428086031994</v>
       </c>
       <c r="I15" s="56">
         <f t="shared" si="2"/>
-        <v>51283.335448799997</v>
+        <v>62377.247872799999</v>
       </c>
       <c r="J15" s="56">
         <f>Edesur!N22</f>
-        <v>28731.127431784007</v>
+        <v>37008.543713280022</v>
       </c>
       <c r="K15" s="56">
         <f t="shared" si="3"/>
@@ -3092,14 +3117,14 @@
       </c>
       <c r="M15" s="57">
         <f t="shared" si="5"/>
-        <v>130414.46751107997</v>
+        <v>279407.3046097632</v>
       </c>
       <c r="O15" s="151">
         <f t="shared" si="6"/>
-        <v>101683.34007929597</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>242398.76089648317</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
         <v>56</v>
       </c>
@@ -3113,11 +3138,11 @@
         <v>5.21</v>
       </c>
       <c r="E16" s="129">
-        <v>107734.41851670001</v>
-      </c>
-      <c r="F16" s="217">
+        <v>134085.060618191</v>
+      </c>
+      <c r="F16" s="232">
         <f t="shared" ref="F16:F21" si="9">E16</f>
-        <v>107734.41851670001</v>
+        <v>134085.060618191</v>
       </c>
       <c r="G16" s="56">
         <f t="shared" si="0"/>
@@ -3129,11 +3154,11 @@
       </c>
       <c r="I16" s="56">
         <f t="shared" si="2"/>
-        <v>53013.130493700002</v>
+        <v>64481.242344700004</v>
       </c>
       <c r="J16" s="56">
         <f>Edesur!N23</f>
-        <v>34945.233678490978</v>
+        <v>42740.815402219974</v>
       </c>
       <c r="K16" s="56">
         <f t="shared" si="3"/>
@@ -3145,15 +3170,15 @@
       </c>
       <c r="M16" s="57">
         <f t="shared" si="5"/>
-        <v>140058.36417219098</v>
+        <v>159322.05774691998</v>
       </c>
       <c r="N16" s="44"/>
       <c r="O16" s="151">
         <f t="shared" si="6"/>
-        <v>105113.13049370001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+        <v>116581.2423447</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>59</v>
       </c>
@@ -3165,11 +3190,11 @@
         <v>5.04</v>
       </c>
       <c r="E17" s="129">
-        <v>104219.09200080001</v>
-      </c>
-      <c r="F17" s="217">
+        <v>121859.97038458401</v>
+      </c>
+      <c r="F17" s="232">
         <f t="shared" si="9"/>
-        <v>104219.09200080001</v>
+        <v>121859.97038458401</v>
       </c>
       <c r="G17" s="56">
         <f t="shared" si="0"/>
@@ -3181,11 +3206,11 @@
       </c>
       <c r="I17" s="56">
         <f t="shared" si="2"/>
-        <v>51283.335448799997</v>
+        <v>62377.247872799999</v>
       </c>
       <c r="J17" s="56">
         <f>Edesur!N24</f>
-        <v>25955.032231784015</v>
+        <v>22330.878213279997</v>
       </c>
       <c r="K17" s="56">
         <f t="shared" si="3"/>
@@ -3197,18 +3222,18 @@
       </c>
       <c r="M17" s="57">
         <f t="shared" si="5"/>
-        <v>127638.36768058402</v>
+        <v>135108.12608607998</v>
       </c>
       <c r="O17" s="151">
         <f t="shared" si="6"/>
-        <v>101683.3354488</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="205" t="s">
+        <v>112777.24787279998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="204" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="206"/>
+      <c r="B18" s="205"/>
       <c r="C18" s="63" t="s">
         <v>62</v>
       </c>
@@ -3216,11 +3241,11 @@
         <v>5.21</v>
       </c>
       <c r="E18" s="129">
-        <v>107734.41851670001</v>
-      </c>
-      <c r="F18" s="217">
+        <v>130961.95351819103</v>
+      </c>
+      <c r="F18" s="232">
         <f t="shared" si="9"/>
-        <v>107734.41851670001</v>
+        <v>130961.95351819103</v>
       </c>
       <c r="G18" s="64">
         <f t="shared" si="0"/>
@@ -3232,11 +3257,11 @@
       </c>
       <c r="I18" s="64">
         <f t="shared" si="2"/>
-        <v>53013.130493700002</v>
+        <v>64481.242344700004</v>
       </c>
       <c r="J18" s="56">
         <f>Edesur!N25</f>
-        <v>31822.126578491028</v>
+        <v>26243.682102220002</v>
       </c>
       <c r="K18" s="64">
         <f t="shared" si="3"/>
@@ -3248,21 +3273,21 @@
       </c>
       <c r="M18" s="57">
         <f t="shared" si="5"/>
-        <v>136935.25707219105</v>
-      </c>
-      <c r="N18" s="208"/>
+        <v>142824.92444691999</v>
+      </c>
+      <c r="N18" s="207"/>
       <c r="O18" s="151">
         <f t="shared" si="6"/>
-        <v>105113.13049370001</v>
-      </c>
-      <c r="P18" s="207"/>
-      <c r="Q18" s="204"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+        <v>116581.24234469999</v>
+      </c>
+      <c r="P18" s="206"/>
+      <c r="Q18" s="203"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="199"/>
+      <c r="B19" s="198"/>
       <c r="C19" s="63" t="s">
         <v>64</v>
       </c>
@@ -3270,11 +3295,11 @@
         <v>7.4</v>
       </c>
       <c r="E19" s="129">
-        <v>153020.095398</v>
-      </c>
-      <c r="F19" s="217">
+        <v>190590.86978054006</v>
+      </c>
+      <c r="F19" s="232">
         <f t="shared" si="9"/>
-        <v>153020.095398</v>
+        <v>190590.86978054006</v>
       </c>
       <c r="G19" s="64">
         <f t="shared" si="0"/>
@@ -3286,11 +3311,11 @@
       </c>
       <c r="I19" s="64">
         <f t="shared" si="2"/>
-        <v>75296.960778000008</v>
+        <v>91585.641717999999</v>
       </c>
       <c r="J19" s="56">
         <f>Edesur!N26</f>
-        <v>49778.063762540056</v>
+        <v>59612.566706799938</v>
       </c>
       <c r="K19" s="64">
         <f t="shared" si="3"/>
@@ -3302,14 +3327,14 @@
       </c>
       <c r="M19" s="57">
         <f t="shared" si="5"/>
-        <v>199075.02454054006</v>
+        <v>225198.20842479993</v>
       </c>
       <c r="O19" s="151">
         <f t="shared" si="6"/>
-        <v>149296.96077800001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="24" x14ac:dyDescent="0.3">
+        <v>165585.641718</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="184"/>
       <c r="B20" s="178" t="s">
         <v>99</v>
@@ -3321,11 +3346,11 @@
         <v>1.08</v>
       </c>
       <c r="E20" s="181">
-        <v>22332.662571600002</v>
-      </c>
-      <c r="F20" s="218">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="F20" s="233">
         <f t="shared" si="9"/>
-        <v>22332.662571600002</v>
+        <v>25590.323225268006</v>
       </c>
       <c r="G20" s="182">
         <f t="shared" si="0"/>
@@ -3334,11 +3359,11 @@
       <c r="H20" s="182"/>
       <c r="I20" s="182">
         <f t="shared" si="2"/>
-        <v>10989.286167600001</v>
+        <v>13366.5531156</v>
       </c>
       <c r="J20" s="182">
         <f>Edesur!N27</f>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="K20" s="182">
         <f t="shared" si="3"/>
@@ -3350,14 +3375,14 @@
       </c>
       <c r="M20" s="183">
         <f t="shared" si="5"/>
-        <v>26828.551217268006</v>
+        <v>28051.386104159999</v>
       </c>
       <c r="O20" s="151">
         <f t="shared" si="6"/>
-        <v>21789.286167600003</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+        <v>24166.5531156</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>57</v>
@@ -3369,11 +3394,11 @@
         <v>1.08</v>
       </c>
       <c r="E21" s="129">
-        <v>22332.662571600002</v>
-      </c>
-      <c r="F21" s="217">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="F21" s="232">
         <f t="shared" si="9"/>
-        <v>22332.662571600002</v>
+        <v>25590.323225268006</v>
       </c>
       <c r="G21" s="56">
         <f t="shared" si="0"/>
@@ -3385,11 +3410,11 @@
       </c>
       <c r="I21" s="56">
         <f t="shared" si="2"/>
-        <v>10989.286167600001</v>
+        <v>13366.5531156</v>
       </c>
       <c r="J21" s="56">
         <f>Edesur!N28</f>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="K21" s="56">
         <f t="shared" si="3"/>
@@ -3401,14 +3426,14 @@
       </c>
       <c r="M21" s="57">
         <f t="shared" si="5"/>
-        <v>26828.551217268006</v>
+        <v>28051.386104159999</v>
       </c>
       <c r="O21" s="151">
         <f t="shared" si="6"/>
-        <v>21789.286167600003</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+        <v>24166.5531156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="139"/>
       <c r="B22" s="140"/>
       <c r="C22" s="141" t="s">
@@ -3418,26 +3443,26 @@
         <v>1.08</v>
       </c>
       <c r="E22" s="143">
-        <v>262598.51501640002</v>
-      </c>
-      <c r="F22" s="219">
+        <v>298692.77884232404</v>
+      </c>
+      <c r="F22" s="234">
         <v>0</v>
       </c>
       <c r="G22" s="144">
         <f t="shared" si="0"/>
-        <v>262598.51501640002</v>
+        <v>298692.77884232404</v>
       </c>
       <c r="H22" s="144">
         <f t="shared" si="1"/>
-        <v>10503.940600656</v>
+        <v>11947.711153692962</v>
       </c>
       <c r="I22" s="144">
         <f t="shared" si="2"/>
-        <v>10989.286167600001</v>
+        <v>13366.5531156</v>
       </c>
       <c r="J22" s="144">
         <f>Edesur!N29</f>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="K22" s="144">
         <f t="shared" si="3"/>
@@ -3449,14 +3474,14 @@
       </c>
       <c r="M22" s="145">
         <f t="shared" si="5"/>
-        <v>299931.00683432404</v>
+        <v>338691.87610017706</v>
       </c>
       <c r="O22" s="151">
         <f t="shared" si="6"/>
-        <v>294891.74178465601</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+        <v>334807.04311161704</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>35</v>
       </c>
@@ -3468,11 +3493,11 @@
         <v>1.08</v>
       </c>
       <c r="E23" s="129">
-        <v>54462.538760400006</v>
-      </c>
-      <c r="F23" s="217">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="F23" s="232">
         <f>E23</f>
-        <v>54462.538760400006</v>
+        <v>25590.323225268006</v>
       </c>
       <c r="G23" s="56">
         <f t="shared" si="0"/>
@@ -3484,11 +3509,11 @@
       </c>
       <c r="I23" s="56">
         <f t="shared" si="2"/>
-        <v>10989.286167600001</v>
+        <v>13366.5531156</v>
       </c>
       <c r="J23" s="56">
         <f>Edesur!N30</f>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="K23" s="56">
         <f t="shared" si="3"/>
@@ -3500,14 +3525,14 @@
       </c>
       <c r="M23" s="57">
         <f t="shared" si="5"/>
-        <v>26828.551217268006</v>
+        <v>28051.386104159999</v>
       </c>
       <c r="O23" s="151">
         <f t="shared" si="6"/>
-        <v>21789.286167600003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+        <v>24166.5531156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>49</v>
       </c>
@@ -3521,11 +3546,11 @@
         <v>1.08</v>
       </c>
       <c r="E24" s="129">
-        <v>22332.662571600002</v>
-      </c>
-      <c r="F24" s="217">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="F24" s="232">
         <f t="shared" ref="F24" si="10">E24</f>
-        <v>22332.662571600002</v>
+        <v>25590.323225268006</v>
       </c>
       <c r="G24" s="56">
         <f t="shared" si="0"/>
@@ -3537,11 +3562,11 @@
       </c>
       <c r="I24" s="56">
         <f t="shared" si="2"/>
-        <v>10989.286167600001</v>
+        <v>13366.5531156</v>
       </c>
       <c r="J24" s="56">
         <f>Edesur!N31</f>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="K24" s="56">
         <f t="shared" si="3"/>
@@ -3553,18 +3578,18 @@
       </c>
       <c r="M24" s="57">
         <f t="shared" si="5"/>
-        <v>26828.551217268006</v>
+        <v>28051.386104159999</v>
       </c>
       <c r="O24" s="151">
         <f t="shared" si="6"/>
-        <v>21789.286167600003</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+        <v>24166.5531156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="199" t="s">
+      <c r="B25" s="198" t="s">
         <v>106</v>
       </c>
       <c r="C25" s="60" t="s">
@@ -3574,11 +3599,11 @@
         <v>1.08</v>
       </c>
       <c r="E25" s="129">
-        <v>78827.255240400002</v>
-      </c>
-      <c r="F25" s="217">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="F25" s="232">
         <f>E25</f>
-        <v>78827.255240400002</v>
+        <v>25590.323225268006</v>
       </c>
       <c r="G25" s="56">
         <f t="shared" si="0"/>
@@ -3590,11 +3615,11 @@
       </c>
       <c r="I25" s="56">
         <f t="shared" si="2"/>
-        <v>10989.286167600001</v>
+        <v>13366.5531156</v>
       </c>
       <c r="J25" s="56">
         <f>Edesur!N32</f>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="K25" s="56">
         <f t="shared" si="3"/>
@@ -3606,14 +3631,14 @@
       </c>
       <c r="M25" s="57">
         <f t="shared" si="5"/>
-        <v>26828.551217268006</v>
+        <v>28051.386104159999</v>
       </c>
       <c r="O25" s="151">
         <f t="shared" si="6"/>
-        <v>21789.286167600003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+        <v>24166.5531156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
         <v>63</v>
       </c>
@@ -3625,11 +3650,11 @@
         <v>1.08</v>
       </c>
       <c r="E26" s="129">
-        <v>22332.662571600002</v>
-      </c>
-      <c r="F26" s="217">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="F26" s="232">
         <f t="shared" ref="F26:F28" si="11">E26</f>
-        <v>22332.662571600002</v>
+        <v>25590.323225268006</v>
       </c>
       <c r="G26" s="56">
         <f t="shared" si="0"/>
@@ -3641,11 +3666,11 @@
       </c>
       <c r="I26" s="56">
         <f t="shared" si="2"/>
-        <v>10989.286167600001</v>
+        <v>13366.5531156</v>
       </c>
       <c r="J26" s="56">
         <f>Edesur!N33</f>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="K26" s="56">
         <f t="shared" si="3"/>
@@ -3657,14 +3682,14 @@
       </c>
       <c r="M26" s="57">
         <f t="shared" si="5"/>
-        <v>26828.551217268006</v>
+        <v>28051.386104159999</v>
       </c>
       <c r="O26" s="151">
         <f t="shared" si="6"/>
-        <v>21789.286167600003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+        <v>24166.5531156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>63</v>
       </c>
@@ -3676,11 +3701,11 @@
         <v>1.08</v>
       </c>
       <c r="E27" s="129">
-        <v>22332.662571600002</v>
-      </c>
-      <c r="F27" s="217">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="F27" s="232">
         <f t="shared" si="11"/>
-        <v>22332.662571600002</v>
+        <v>25590.323225268006</v>
       </c>
       <c r="G27" s="56">
         <f t="shared" si="0"/>
@@ -3692,11 +3717,11 @@
       </c>
       <c r="I27" s="56">
         <f t="shared" si="2"/>
-        <v>10989.286167600001</v>
+        <v>13366.5531156</v>
       </c>
       <c r="J27" s="56">
         <f>Edesur!N34</f>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="K27" s="56">
         <f t="shared" si="3"/>
@@ -3708,18 +3733,18 @@
       </c>
       <c r="M27" s="57">
         <f t="shared" si="5"/>
-        <v>26828.551217268006</v>
+        <v>28051.386104159999</v>
       </c>
       <c r="O27" s="151">
         <f t="shared" si="6"/>
-        <v>21789.286167600003</v>
+        <v>24166.5531156</v>
       </c>
       <c r="P27" s="44">
         <f>F27+F26+F19</f>
-        <v>197685.4205412</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+        <v>241771.51623107606</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="66"/>
       <c r="B28" s="65" t="str">
         <f>B7</f>
@@ -3732,11 +3757,11 @@
         <v>1.08</v>
       </c>
       <c r="E28" s="129">
-        <v>22332.662571600002</v>
-      </c>
-      <c r="F28" s="217">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="F28" s="232">
         <f t="shared" si="11"/>
-        <v>22332.662571600002</v>
+        <v>25590.323225268006</v>
       </c>
       <c r="G28" s="56">
         <f t="shared" si="0"/>
@@ -3748,11 +3773,11 @@
       </c>
       <c r="I28" s="56">
         <f t="shared" si="2"/>
-        <v>10989.286167600001</v>
+        <v>13366.5531156</v>
       </c>
       <c r="J28" s="56">
         <f>Edesur!N35</f>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="K28" s="56">
         <f t="shared" si="3"/>
@@ -3764,14 +3789,14 @@
       </c>
       <c r="M28" s="57">
         <f t="shared" si="5"/>
-        <v>26828.551217268006</v>
+        <v>28051.386104159999</v>
       </c>
       <c r="O28" s="151">
         <f t="shared" si="6"/>
-        <v>21789.286167600003</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+        <v>24166.5531156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="66" t="s">
         <v>53</v>
       </c>
@@ -3785,27 +3810,24 @@
         <v>1.08</v>
       </c>
       <c r="E29" s="129">
-        <v>22332.662571600002</v>
-      </c>
-      <c r="F29" s="217">
-        <f>E29</f>
-        <v>22332.662571600002</v>
-      </c>
+        <v>25590.323225268006</v>
+      </c>
+      <c r="F29" s="210"/>
       <c r="G29" s="56">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25590.323225268006</v>
       </c>
       <c r="H29" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1023.6129290107202</v>
       </c>
       <c r="I29" s="56">
         <f t="shared" si="2"/>
-        <v>10989.286167600001</v>
+        <v>13366.5531156</v>
       </c>
       <c r="J29" s="56">
         <f>Edesur!N36</f>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="K29" s="56">
         <f t="shared" si="3"/>
@@ -3817,14 +3839,14 @@
       </c>
       <c r="M29" s="57">
         <f t="shared" si="5"/>
-        <v>26828.551217268006</v>
+        <v>54665.322258438733</v>
       </c>
       <c r="O29" s="151">
         <f t="shared" si="6"/>
-        <v>21789.286167600003</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+        <v>50780.48926987873</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="68"/>
@@ -3839,7 +3861,7 @@
       <c r="L30" s="71"/>
       <c r="M30" s="71"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="72"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74" t="s">
@@ -3852,13 +3874,13 @@
       <c r="E31" s="73"/>
       <c r="F31" s="135">
         <f>SUM(F3:F30)</f>
-        <v>2610074.1626310009</v>
+        <v>2466028.3590707099</v>
       </c>
       <c r="G31" s="75"/>
       <c r="H31" s="75"/>
       <c r="I31" s="136">
         <f>SUM(I3:I30)</f>
-        <v>1017526.4969999997</v>
+        <v>1237643.8070000003</v>
       </c>
       <c r="J31" s="136"/>
       <c r="K31" s="136">
@@ -3868,75 +3890,75 @@
       <c r="L31" s="135"/>
       <c r="M31" s="135">
         <f>SUM(M3:M29)</f>
-        <v>3055511.7131784861</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+        <v>3398007.4200824555</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K32" s="22"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="230" t="s">
-        <v>111</v>
-      </c>
-      <c r="B33" s="230"/>
-      <c r="C33" s="230"/>
-      <c r="D33" s="230"/>
-      <c r="E33" s="230"/>
-      <c r="F33" s="230"/>
-      <c r="G33" s="230"/>
-      <c r="H33" s="230"/>
-      <c r="I33" s="230"/>
-      <c r="J33" s="230"/>
-      <c r="K33" s="230"/>
-      <c r="L33" s="230"/>
-      <c r="M33" s="230"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="230"/>
-      <c r="B34" s="230"/>
-      <c r="C34" s="230"/>
-      <c r="D34" s="230"/>
-      <c r="E34" s="230"/>
-      <c r="F34" s="230"/>
-      <c r="G34" s="230"/>
-      <c r="H34" s="230"/>
-      <c r="I34" s="230"/>
-      <c r="J34" s="230"/>
-      <c r="K34" s="230"/>
-      <c r="L34" s="230"/>
-      <c r="M34" s="230"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="230"/>
-      <c r="B35" s="230"/>
-      <c r="C35" s="230"/>
-      <c r="D35" s="230"/>
-      <c r="E35" s="230"/>
-      <c r="F35" s="230"/>
-      <c r="G35" s="230"/>
-      <c r="H35" s="230"/>
-      <c r="I35" s="230"/>
-      <c r="J35" s="230"/>
-      <c r="K35" s="230"/>
-      <c r="L35" s="230"/>
-      <c r="M35" s="230"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="230"/>
-      <c r="B36" s="230"/>
-      <c r="C36" s="230"/>
-      <c r="D36" s="230"/>
-      <c r="E36" s="230"/>
-      <c r="F36" s="230"/>
-      <c r="G36" s="230"/>
-      <c r="H36" s="230"/>
-      <c r="I36" s="230"/>
-      <c r="J36" s="230"/>
-      <c r="K36" s="230"/>
-      <c r="L36" s="230"/>
-      <c r="M36" s="230"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="223" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="223"/>
+      <c r="C33" s="223"/>
+      <c r="D33" s="223"/>
+      <c r="E33" s="223"/>
+      <c r="F33" s="223"/>
+      <c r="G33" s="223"/>
+      <c r="H33" s="223"/>
+      <c r="I33" s="223"/>
+      <c r="J33" s="223"/>
+      <c r="K33" s="223"/>
+      <c r="L33" s="223"/>
+      <c r="M33" s="223"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="223"/>
+      <c r="B34" s="223"/>
+      <c r="C34" s="223"/>
+      <c r="D34" s="223"/>
+      <c r="E34" s="223"/>
+      <c r="F34" s="223"/>
+      <c r="G34" s="223"/>
+      <c r="H34" s="223"/>
+      <c r="I34" s="223"/>
+      <c r="J34" s="223"/>
+      <c r="K34" s="223"/>
+      <c r="L34" s="223"/>
+      <c r="M34" s="223"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="223"/>
+      <c r="B35" s="223"/>
+      <c r="C35" s="223"/>
+      <c r="D35" s="223"/>
+      <c r="E35" s="223"/>
+      <c r="F35" s="223"/>
+      <c r="G35" s="223"/>
+      <c r="H35" s="223"/>
+      <c r="I35" s="223"/>
+      <c r="J35" s="223"/>
+      <c r="K35" s="223"/>
+      <c r="L35" s="223"/>
+      <c r="M35" s="223"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="223"/>
+      <c r="B36" s="223"/>
+      <c r="C36" s="223"/>
+      <c r="D36" s="223"/>
+      <c r="E36" s="223"/>
+      <c r="F36" s="223"/>
+      <c r="G36" s="223"/>
+      <c r="H36" s="223"/>
+      <c r="I36" s="223"/>
+      <c r="J36" s="223"/>
+      <c r="K36" s="223"/>
+      <c r="L36" s="223"/>
+      <c r="M36" s="223"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -3956,45 +3978,45 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="233" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="226" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="234"/>
-      <c r="C1" s="234"/>
-      <c r="D1" s="234"/>
-      <c r="E1" s="234"/>
-      <c r="F1" s="234"/>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
-      <c r="L1" s="234"/>
-      <c r="M1" s="234"/>
-      <c r="N1" s="235"/>
+      <c r="B1" s="227"/>
+      <c r="C1" s="227"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="227"/>
+      <c r="M1" s="227"/>
+      <c r="N1" s="228"/>
       <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
       <c r="C2" s="161"/>
@@ -4012,7 +4034,7 @@
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
       <c r="C3" s="163"/>
@@ -4030,7 +4052,7 @@
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
       <c r="C4" s="163"/>
@@ -4050,7 +4072,7 @@
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
       <c r="C5" s="163"/>
@@ -4068,10 +4090,10 @@
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
-      <c r="C6" s="216" t="str">
+      <c r="C6" s="209" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 15/01</v>
       </c>
@@ -4089,12 +4111,12 @@
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81"/>
       <c r="B7" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="214">
         <v>666521.55000000005</v>
       </c>
       <c r="D7" s="28"/>
@@ -4116,7 +4138,7 @@
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81"/>
       <c r="B8" s="80" t="s">
         <v>77</v>
@@ -4130,18 +4152,18 @@
       <c r="J8" s="78"/>
       <c r="K8" s="86">
         <f>C8-J38</f>
-        <v>-199922.9342899998</v>
-      </c>
-      <c r="L8" s="237">
+        <v>-306814.79180000001</v>
+      </c>
+      <c r="L8" s="230">
         <f>C7-J38</f>
-        <v>466598.61571000027</v>
-      </c>
-      <c r="M8" s="237"/>
+        <v>359706.75820000004</v>
+      </c>
+      <c r="M8" s="230"/>
       <c r="N8" s="84"/>
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="87" t="s">
         <v>78</v>
       </c>
@@ -4186,7 +4208,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="98">
         <v>1</v>
       </c>
@@ -4203,46 +4225,46 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F10" s="103">
-        <v>4302.83</v>
+        <v>4441.7</v>
       </c>
       <c r="G10" s="103">
-        <v>4441.7</v>
+        <v>4657.8999999999996</v>
       </c>
       <c r="H10" s="104">
         <f>G10-F10</f>
-        <v>138.86999999999989</v>
+        <v>216.19999999999982</v>
       </c>
       <c r="I10" s="105">
         <f t="shared" ref="I10:I37" si="0">H10*7%</f>
-        <v>9.7208999999999932</v>
+        <v>15.133999999999988</v>
       </c>
       <c r="J10" s="116">
         <f>M10*93.787</f>
-        <v>13024.200689999991</v>
+        <v>20276.749399999986</v>
       </c>
       <c r="K10" s="106">
         <f>K8*E10%</f>
-        <v>-10216.061942218992</v>
+        <v>-15678.235860980003</v>
       </c>
       <c r="L10" s="127">
         <f>L$8*E10/S$12</f>
-        <v>23843.189262781016</v>
+        <v>18381.015344020001</v>
       </c>
       <c r="M10" s="107">
         <f>G10-F10</f>
-        <v>138.86999999999989</v>
+        <v>216.19999999999982</v>
       </c>
       <c r="N10" s="104">
         <f>J10+L10</f>
-        <v>36867.389952781006</v>
+        <v>38657.764744019987</v>
       </c>
       <c r="O10" s="97">
         <f>N10+'prorrateo '!M3</f>
-        <v>176830.38390226199</v>
+        <v>191659.12802573998</v>
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="99">
         <v>2</v>
       </c>
@@ -4259,46 +4281,46 @@
         <v>5.09</v>
       </c>
       <c r="F11" s="103">
-        <v>4106.5</v>
+        <v>4207.8</v>
       </c>
       <c r="G11" s="103">
-        <v>4207.8</v>
+        <v>4378</v>
       </c>
       <c r="H11" s="104">
         <f t="shared" ref="H11:H27" si="1">G11-F11</f>
-        <v>101.30000000000018</v>
+        <v>170.19999999999982</v>
       </c>
       <c r="I11" s="105">
         <f t="shared" si="0"/>
-        <v>7.0910000000000135</v>
+        <v>11.913999999999989</v>
       </c>
       <c r="J11" s="116">
         <f t="shared" ref="J11:J26" si="2">M11*93.787</f>
-        <v>9500.6231000000171</v>
+        <v>15962.547399999983</v>
       </c>
       <c r="K11" s="106">
         <f>K8*E11%</f>
-        <v>-10176.077355360991</v>
+        <v>-15616.87290262</v>
       </c>
       <c r="L11" s="127">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>23749.869539639014</v>
+        <v>18309.073992380003</v>
       </c>
       <c r="M11" s="107">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
-        <v>101.30000000000018</v>
+        <v>170.19999999999982</v>
       </c>
       <c r="N11" s="104">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>33250.492639639029</v>
+        <v>34271.621392379988</v>
       </c>
       <c r="O11" s="97">
         <f>N11+'prorrateo '!M4</f>
-        <v>169193.08397657805</v>
+        <v>182439.31256105995</v>
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="98">
         <v>3</v>
       </c>
@@ -4315,49 +4337,49 @@
         <v>5.04</v>
       </c>
       <c r="F12" s="103">
-        <v>1558.7</v>
+        <v>1667.5</v>
       </c>
       <c r="G12" s="103">
-        <v>1667.5</v>
+        <v>1981.8</v>
       </c>
       <c r="H12" s="104">
         <f t="shared" si="1"/>
-        <v>108.79999999999995</v>
+        <v>314.29999999999995</v>
       </c>
       <c r="I12" s="105">
         <f t="shared" si="0"/>
-        <v>7.6159999999999979</v>
+        <v>22.000999999999998</v>
       </c>
       <c r="J12" s="116">
         <f t="shared" si="2"/>
-        <v>10204.025599999997</v>
+        <v>29477.254099999998</v>
       </c>
       <c r="K12" s="106">
         <f>K8*E12%</f>
-        <v>-10076.115888215991</v>
+        <v>-15463.46550672</v>
       </c>
       <c r="L12" s="127">
         <f t="shared" si="3"/>
-        <v>23516.570231784015</v>
+        <v>18129.220613280002</v>
       </c>
       <c r="M12" s="107">
         <f>G12-F12</f>
-        <v>108.79999999999995</v>
+        <v>314.29999999999995</v>
       </c>
       <c r="N12" s="104">
         <f t="shared" si="5"/>
-        <v>33720.595831784012</v>
+        <v>47606.474713279997</v>
       </c>
       <c r="O12" s="97">
         <f>N12+'prorrateo '!M5</f>
-        <v>200225.7219868321</v>
+        <v>235359.93146704871</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="98">
         <v>4</v>
       </c>
@@ -4374,46 +4396,46 @@
         <v>5.21</v>
       </c>
       <c r="F13" s="103">
-        <v>1204.5999999999999</v>
+        <v>1283.0999999999999</v>
       </c>
       <c r="G13" s="103">
-        <v>1283.0999999999999</v>
+        <v>1453</v>
       </c>
       <c r="H13" s="104">
         <f t="shared" si="1"/>
-        <v>78.5</v>
+        <v>169.90000000000009</v>
       </c>
       <c r="I13" s="166">
         <f t="shared" si="0"/>
-        <v>5.4950000000000001</v>
+        <v>11.893000000000008</v>
       </c>
       <c r="J13" s="116">
         <f t="shared" si="2"/>
-        <v>7362.2795000000006</v>
+        <v>15934.411300000009</v>
       </c>
       <c r="K13" s="167">
         <f>K8*E13%</f>
-        <v>-10415.98487650899</v>
+        <v>-15985.050652780001</v>
       </c>
       <c r="L13" s="127">
         <f t="shared" si="3"/>
-        <v>24309.787878491014</v>
+        <v>18740.722102220003</v>
       </c>
       <c r="M13" s="168">
         <f t="shared" si="4"/>
-        <v>78.5</v>
+        <v>169.90000000000009</v>
       </c>
       <c r="N13" s="104">
         <f t="shared" si="5"/>
-        <v>31672.067378491014</v>
+        <v>34675.13340222001</v>
       </c>
       <c r="O13" s="97">
         <f>N13+'prorrateo '!M6</f>
-        <v>280501.06050805002</v>
+        <v>185931.50914914001</v>
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="98">
         <v>6</v>
       </c>
@@ -4430,46 +4452,46 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F14" s="103">
-        <v>1814</v>
+        <v>1914.3</v>
       </c>
       <c r="G14" s="103">
-        <v>1914.3</v>
+        <v>2130</v>
       </c>
       <c r="H14" s="104">
         <f t="shared" si="1"/>
-        <v>100.29999999999995</v>
+        <v>215.70000000000005</v>
       </c>
       <c r="I14" s="105">
         <f t="shared" si="0"/>
-        <v>7.0209999999999972</v>
+        <v>15.099000000000004</v>
       </c>
       <c r="J14" s="116">
         <f t="shared" si="2"/>
-        <v>9406.8360999999968</v>
+        <v>20229.855900000006</v>
       </c>
       <c r="K14" s="106">
         <f>K8*E14%</f>
-        <v>-10216.061942218992</v>
+        <v>-15678.235860980003</v>
       </c>
       <c r="L14" s="127">
         <f t="shared" si="3"/>
-        <v>23843.189262781016</v>
+        <v>18381.015344020001</v>
       </c>
       <c r="M14" s="107">
         <f t="shared" si="4"/>
-        <v>100.29999999999995</v>
+        <v>215.70000000000005</v>
       </c>
       <c r="N14" s="104">
         <f t="shared" si="5"/>
-        <v>33250.025362781016</v>
+        <v>38610.871244020003</v>
       </c>
       <c r="O14" s="97">
         <f>N14+'prorrateo '!M7</f>
-        <v>169595.65472226203</v>
+        <v>191565.34102574002</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="98">
         <v>7</v>
       </c>
@@ -4486,45 +4508,45 @@
         <v>5.09</v>
       </c>
       <c r="F15" s="103">
-        <v>3018</v>
+        <v>3098.9</v>
       </c>
       <c r="G15" s="103">
-        <v>3098.9</v>
+        <v>3326.8</v>
       </c>
       <c r="H15" s="104">
         <f t="shared" si="1"/>
-        <v>80.900000000000091</v>
+        <v>227.90000000000009</v>
       </c>
       <c r="I15" s="105">
         <f t="shared" si="0"/>
-        <v>5.6630000000000065</v>
+        <v>15.953000000000008</v>
       </c>
       <c r="J15" s="116">
         <f t="shared" si="2"/>
-        <v>7587.3683000000092</v>
+        <v>21374.057300000011</v>
       </c>
       <c r="K15" s="106">
         <f>K8*E15%</f>
-        <v>-10176.077355360991</v>
+        <v>-15616.87290262</v>
       </c>
       <c r="L15" s="127">
         <f t="shared" si="3"/>
-        <v>23749.869539639014</v>
+        <v>18309.073992380003</v>
       </c>
       <c r="M15" s="107">
         <f t="shared" si="4"/>
-        <v>80.900000000000091</v>
+        <v>227.90000000000009</v>
       </c>
       <c r="N15" s="104">
         <f t="shared" si="5"/>
-        <v>31337.237839639023</v>
+        <v>39683.131292380014</v>
       </c>
       <c r="O15" s="97">
         <f>N15+'prorrateo '!M8</f>
-        <v>165366.57437657804</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+        <v>193262.33236106002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="98">
         <v>8</v>
       </c>
@@ -4541,45 +4563,45 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F16" s="103">
-        <v>2516.4</v>
+        <v>2607.6</v>
       </c>
       <c r="G16" s="103">
-        <v>2607.6</v>
+        <v>2744.5</v>
       </c>
       <c r="H16" s="104">
         <f t="shared" si="1"/>
-        <v>91.199999999999818</v>
+        <v>136.90000000000009</v>
       </c>
       <c r="I16" s="105">
         <f t="shared" si="0"/>
-        <v>6.3839999999999879</v>
+        <v>9.5830000000000073</v>
       </c>
       <c r="J16" s="116">
         <f t="shared" si="2"/>
-        <v>8553.3743999999842</v>
+        <v>12839.440300000009</v>
       </c>
       <c r="K16" s="106">
         <f>K8*E16%</f>
-        <v>-10216.061942218992</v>
+        <v>-15678.235860980003</v>
       </c>
       <c r="L16" s="127">
         <f t="shared" si="3"/>
-        <v>23843.189262781016</v>
+        <v>18381.015344020001</v>
       </c>
       <c r="M16" s="107">
         <f t="shared" si="4"/>
-        <v>91.199999999999818</v>
+        <v>136.90000000000009</v>
       </c>
       <c r="N16" s="104">
         <f t="shared" si="5"/>
-        <v>32396.563662781002</v>
+        <v>31220.45564402001</v>
       </c>
       <c r="O16" s="97">
         <f>N16+'prorrateo '!M9</f>
-        <v>167888.731322262</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>176418.02467122104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="98">
         <v>9</v>
       </c>
@@ -4595,46 +4617,46 @@
       <c r="E17" s="187">
         <v>5.09</v>
       </c>
-      <c r="F17" s="189">
-        <v>3375.8</v>
-      </c>
-      <c r="G17" s="189">
+      <c r="F17" s="188">
         <v>3400.1</v>
       </c>
-      <c r="H17" s="190">
+      <c r="G17" s="188">
+        <v>3430.2</v>
+      </c>
+      <c r="H17" s="189">
         <f t="shared" si="1"/>
-        <v>24.299999999999727</v>
-      </c>
-      <c r="I17" s="191">
+        <v>30.099999999999909</v>
+      </c>
+      <c r="I17" s="190">
         <f t="shared" si="0"/>
-        <v>1.700999999999981</v>
-      </c>
-      <c r="J17" s="192">
+        <v>2.106999999999994</v>
+      </c>
+      <c r="J17" s="191">
         <f t="shared" si="2"/>
-        <v>2279.0240999999746</v>
-      </c>
-      <c r="K17" s="193">
+        <v>2822.9886999999917</v>
+      </c>
+      <c r="K17" s="192">
         <f>K8*E17%</f>
-        <v>-10176.077355360991</v>
-      </c>
-      <c r="L17" s="194">
+        <v>-15616.87290262</v>
+      </c>
+      <c r="L17" s="193">
         <f t="shared" si="3"/>
-        <v>23749.869539639014</v>
-      </c>
-      <c r="M17" s="195">
+        <v>18309.073992380003</v>
+      </c>
+      <c r="M17" s="194">
         <f t="shared" si="4"/>
-        <v>24.299999999999727</v>
-      </c>
-      <c r="N17" s="190">
+        <v>30.099999999999909</v>
+      </c>
+      <c r="N17" s="189">
         <f t="shared" si="5"/>
-        <v>26028.893639638987</v>
+        <v>21132.062692379994</v>
       </c>
       <c r="O17" s="97">
         <f>N17+'prorrateo '!M10</f>
-        <v>154749.88597657796</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>156160.19516105996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="98">
         <v>10</v>
       </c>
@@ -4651,45 +4673,45 @@
         <v>5.04</v>
       </c>
       <c r="F18" s="103">
-        <v>2270.5</v>
+        <v>2354.6999999999998</v>
       </c>
       <c r="G18" s="103">
-        <v>2354.6999999999998</v>
+        <v>2485.1</v>
       </c>
       <c r="H18" s="104">
         <f t="shared" si="1"/>
-        <v>84.199999999999818</v>
+        <v>130.40000000000009</v>
       </c>
       <c r="I18" s="105">
         <f t="shared" si="0"/>
-        <v>5.8939999999999877</v>
+        <v>9.1280000000000072</v>
       </c>
       <c r="J18" s="116">
         <f t="shared" si="2"/>
-        <v>7896.8653999999833</v>
+        <v>12229.824800000009</v>
       </c>
       <c r="K18" s="106">
         <f>K8*E18%</f>
-        <v>-10076.115888215991</v>
+        <v>-15463.46550672</v>
       </c>
       <c r="L18" s="127">
         <f t="shared" si="3"/>
-        <v>23516.570231784015</v>
+        <v>18129.220613280002</v>
       </c>
       <c r="M18" s="107">
         <f t="shared" si="4"/>
-        <v>84.199999999999818</v>
+        <v>130.40000000000009</v>
       </c>
       <c r="N18" s="104">
         <f t="shared" si="5"/>
-        <v>31413.435631783999</v>
+        <v>30359.045413280011</v>
       </c>
       <c r="O18" s="97">
         <f>N18+'prorrateo '!M11</f>
-        <v>164510.206712368</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>173495.33869936003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="98">
         <v>11</v>
       </c>
@@ -4706,45 +4728,45 @@
         <v>5.21</v>
       </c>
       <c r="F19" s="103">
-        <v>4351.6000000000004</v>
+        <v>4574.8999999999996</v>
       </c>
       <c r="G19" s="103">
-        <v>4574.8999999999996</v>
+        <v>4913.8</v>
       </c>
       <c r="H19" s="104">
         <f t="shared" si="1"/>
-        <v>223.29999999999927</v>
+        <v>338.90000000000055</v>
       </c>
       <c r="I19" s="105">
         <f t="shared" si="0"/>
-        <v>15.63099999999995</v>
+        <v>23.723000000000042</v>
       </c>
       <c r="J19" s="116">
         <f t="shared" si="2"/>
-        <v>20942.637099999934</v>
+        <v>31784.414300000055</v>
       </c>
       <c r="K19" s="106">
         <f>K8*E19%</f>
-        <v>-10415.98487650899</v>
+        <v>-15985.050652780001</v>
       </c>
       <c r="L19" s="127">
         <f t="shared" si="3"/>
-        <v>24309.787878491014</v>
+        <v>18740.722102220003</v>
       </c>
       <c r="M19" s="107">
         <f>G19-F19</f>
-        <v>223.29999999999927</v>
+        <v>338.90000000000055</v>
       </c>
       <c r="N19" s="104">
         <f t="shared" si="5"/>
-        <v>45252.424978490948</v>
+        <v>50525.136402220058</v>
       </c>
       <c r="O19" s="97">
         <f>N19+'prorrateo '!M12</f>
-        <v>195617.98045068191</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>217631.51514914012</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="98">
         <v>12</v>
       </c>
@@ -4761,100 +4783,100 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F20" s="103">
-        <v>5489.3</v>
+        <v>6064.7</v>
       </c>
       <c r="G20" s="103">
-        <v>6064.7</v>
+        <v>6379</v>
       </c>
       <c r="H20" s="104">
         <f t="shared" si="1"/>
-        <v>575.39999999999964</v>
+        <v>314.30000000000018</v>
       </c>
       <c r="I20" s="105">
         <f t="shared" si="0"/>
-        <v>40.277999999999977</v>
+        <v>22.001000000000015</v>
       </c>
       <c r="J20" s="116">
         <f t="shared" si="2"/>
-        <v>53965.03979999997</v>
+        <v>29477.25410000002</v>
       </c>
       <c r="K20" s="106">
         <f>K8*E20%</f>
-        <v>-10216.061942218992</v>
+        <v>-15678.235860980003</v>
       </c>
       <c r="L20" s="127">
         <f t="shared" si="3"/>
-        <v>23843.189262781016</v>
+        <v>18381.015344020001</v>
       </c>
       <c r="M20" s="107">
         <f t="shared" si="4"/>
-        <v>575.39999999999964</v>
+        <v>314.30000000000018</v>
       </c>
       <c r="N20" s="104">
         <f t="shared" si="5"/>
-        <v>77808.229062780985</v>
+        <v>47858.269444020021</v>
       </c>
       <c r="O20" s="97">
         <f>N20+'prorrateo '!M13</f>
-        <v>258712.06212226197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>210060.13742574007</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="98">
         <v>13</v>
       </c>
       <c r="B21" s="89">
         <v>13</v>
       </c>
-      <c r="C21" s="209" t="s">
+      <c r="C21" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="210" t="s">
+      <c r="D21" s="100" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="211">
+      <c r="E21" s="101">
         <v>5.09</v>
       </c>
-      <c r="F21" s="212">
-        <v>4112.1000000000004</v>
-      </c>
-      <c r="G21" s="212">
+      <c r="F21" s="103">
         <v>4199</v>
       </c>
-      <c r="H21" s="147">
+      <c r="G21" s="103">
+        <v>4271.8</v>
+      </c>
+      <c r="H21" s="104">
         <f t="shared" si="1"/>
-        <v>86.899999999999636</v>
-      </c>
-      <c r="I21" s="213">
+        <v>72.800000000000182</v>
+      </c>
+      <c r="I21" s="105">
         <f t="shared" si="0"/>
-        <v>6.0829999999999753</v>
-      </c>
-      <c r="J21" s="214">
+        <v>5.0960000000000134</v>
+      </c>
+      <c r="J21" s="116">
         <f t="shared" si="2"/>
-        <v>8150.0902999999662</v>
-      </c>
-      <c r="K21" s="148">
+        <v>6827.6936000000178</v>
+      </c>
+      <c r="K21" s="106">
         <f>K8*E21%</f>
-        <v>-10176.077355360991</v>
-      </c>
-      <c r="L21" s="149">
+        <v>-15616.87290262</v>
+      </c>
+      <c r="L21" s="127">
         <f t="shared" si="3"/>
-        <v>23749.869539639014</v>
-      </c>
-      <c r="M21" s="150">
+        <v>18309.073992380003</v>
+      </c>
+      <c r="M21" s="107">
         <f t="shared" si="4"/>
-        <v>86.899999999999636</v>
-      </c>
-      <c r="N21" s="147">
+        <v>72.800000000000182</v>
+      </c>
+      <c r="N21" s="104">
         <f t="shared" si="5"/>
-        <v>31899.959839638981</v>
+        <v>25136.76759238002</v>
       </c>
       <c r="O21" s="97">
         <f>N21+'prorrateo '!M14</f>
-        <v>121708.23417567795</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>164132.47985636702</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="98">
         <v>14</v>
       </c>
@@ -4871,45 +4893,45 @@
         <v>5.04</v>
       </c>
       <c r="F22" s="103">
-        <v>2441.5</v>
+        <v>2497.1</v>
       </c>
       <c r="G22" s="103">
-        <v>2497.1</v>
+        <v>2698.4</v>
       </c>
       <c r="H22" s="104">
         <f t="shared" si="1"/>
-        <v>55.599999999999909</v>
+        <v>201.30000000000018</v>
       </c>
       <c r="I22" s="105">
         <f t="shared" si="0"/>
-        <v>3.8919999999999941</v>
+        <v>14.091000000000014</v>
       </c>
       <c r="J22" s="116">
         <f t="shared" si="2"/>
-        <v>5214.557199999992</v>
+        <v>18879.32310000002</v>
       </c>
       <c r="K22" s="106">
         <f>K8*E22%</f>
-        <v>-10076.115888215991</v>
+        <v>-15463.46550672</v>
       </c>
       <c r="L22" s="127">
         <f t="shared" si="3"/>
-        <v>23516.570231784015</v>
+        <v>18129.220613280002</v>
       </c>
       <c r="M22" s="107">
         <f t="shared" si="4"/>
-        <v>55.599999999999909</v>
+        <v>201.30000000000018</v>
       </c>
       <c r="N22" s="104">
         <f t="shared" si="5"/>
-        <v>28731.127431784007</v>
+        <v>37008.543713280022</v>
       </c>
       <c r="O22" s="97">
         <f>N22+'prorrateo '!M15</f>
-        <v>159145.59494286397</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>316415.8483230432</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="98">
         <v>15</v>
       </c>
@@ -4926,45 +4948,45 @@
         <v>5.21</v>
       </c>
       <c r="F23" s="103">
-        <v>4886.6000000000004</v>
+        <v>5000</v>
       </c>
       <c r="G23" s="103">
-        <v>5000</v>
+        <v>5255.9</v>
       </c>
       <c r="H23" s="104">
         <f t="shared" si="1"/>
-        <v>113.39999999999964</v>
+        <v>255.89999999999964</v>
       </c>
       <c r="I23" s="105">
         <f t="shared" si="0"/>
-        <v>7.9379999999999749</v>
+        <v>17.912999999999975</v>
       </c>
       <c r="J23" s="116">
         <f t="shared" si="2"/>
-        <v>10635.445799999967</v>
+        <v>24000.093299999968</v>
       </c>
       <c r="K23" s="106">
         <f>K8*E23%</f>
-        <v>-10415.98487650899</v>
+        <v>-15985.050652780001</v>
       </c>
       <c r="L23" s="127">
         <f t="shared" si="3"/>
-        <v>24309.787878491014</v>
+        <v>18740.722102220003</v>
       </c>
       <c r="M23" s="107">
         <f t="shared" si="4"/>
-        <v>113.39999999999964</v>
+        <v>255.89999999999964</v>
       </c>
       <c r="N23" s="104">
         <f t="shared" si="5"/>
-        <v>34945.233678490978</v>
+        <v>42740.815402219974</v>
       </c>
       <c r="O23" s="97">
         <f>N23+'prorrateo '!M16</f>
-        <v>175003.59785068195</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>202062.87314913995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="98">
         <v>16</v>
       </c>
@@ -4981,45 +5003,45 @@
         <v>5.04</v>
       </c>
       <c r="F24" s="103">
-        <v>1776.7</v>
+        <v>1802.7</v>
       </c>
       <c r="G24" s="103">
-        <v>1802.7</v>
+        <v>1847.5</v>
       </c>
       <c r="H24" s="104">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>44.799999999999955</v>
       </c>
       <c r="I24" s="105">
         <f t="shared" si="0"/>
-        <v>1.8200000000000003</v>
+        <v>3.135999999999997</v>
       </c>
       <c r="J24" s="116">
         <f t="shared" si="2"/>
-        <v>2438.462</v>
+        <v>4201.6575999999959</v>
       </c>
       <c r="K24" s="106">
         <f>K8*E24%</f>
-        <v>-10076.115888215991</v>
+        <v>-15463.46550672</v>
       </c>
       <c r="L24" s="127">
         <f t="shared" si="3"/>
-        <v>23516.570231784015</v>
+        <v>18129.220613280002</v>
       </c>
       <c r="M24" s="107">
         <f t="shared" si="4"/>
-        <v>26</v>
+        <v>44.799999999999955</v>
       </c>
       <c r="N24" s="104">
         <f t="shared" si="5"/>
-        <v>25955.032231784015</v>
+        <v>22330.878213279997</v>
       </c>
       <c r="O24" s="97">
         <f>N24+'prorrateo '!M17</f>
-        <v>153593.39991236804</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>157439.00429935998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="98">
         <v>17</v>
       </c>
@@ -5036,45 +5058,46 @@
         <v>5.21</v>
       </c>
       <c r="F25" s="103">
-        <v>1869.3</v>
+        <v>1949.4</v>
       </c>
       <c r="G25" s="103">
-        <v>1949.4</v>
+        <f>F25+80</f>
+        <v>2029.4</v>
       </c>
       <c r="H25" s="104">
         <f t="shared" si="1"/>
-        <v>80.100000000000136</v>
+        <v>80</v>
       </c>
       <c r="I25" s="105">
         <f t="shared" si="0"/>
-        <v>5.60700000000001</v>
+        <v>5.6000000000000005</v>
       </c>
       <c r="J25" s="116">
         <f t="shared" si="2"/>
-        <v>7512.338700000013</v>
+        <v>7502.9600000000009</v>
       </c>
       <c r="K25" s="106">
         <f>K8*E25%</f>
-        <v>-10415.98487650899</v>
+        <v>-15985.050652780001</v>
       </c>
       <c r="L25" s="127">
         <f t="shared" si="3"/>
-        <v>24309.787878491014</v>
+        <v>18740.722102220003</v>
       </c>
       <c r="M25" s="107">
         <f t="shared" si="4"/>
-        <v>80.100000000000136</v>
+        <v>80</v>
       </c>
       <c r="N25" s="104">
         <f t="shared" si="5"/>
-        <v>31822.126578491028</v>
+        <v>26243.682102220002</v>
       </c>
       <c r="O25" s="97">
         <f>N25+'prorrateo '!M18</f>
-        <v>168757.38365068208</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>169068.60654914001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="98">
         <v>18</v>
       </c>
@@ -5091,87 +5114,87 @@
         <v>7.4</v>
       </c>
       <c r="F26" s="103">
-        <v>8914.5</v>
+        <v>9077.1</v>
       </c>
       <c r="G26" s="103">
-        <v>9077.1</v>
+        <v>9428.9</v>
       </c>
       <c r="H26" s="104">
         <f t="shared" si="1"/>
-        <v>162.60000000000036</v>
+        <v>351.79999999999927</v>
       </c>
       <c r="I26" s="105">
         <f t="shared" si="0"/>
-        <v>11.382000000000026</v>
+        <v>24.625999999999951</v>
       </c>
       <c r="J26" s="116">
         <f t="shared" si="2"/>
-        <v>15249.766200000035</v>
+        <v>32994.266599999937</v>
       </c>
       <c r="K26" s="106">
         <f>K8*E26%</f>
-        <v>-14794.297137459987</v>
+        <v>-22704.294593200004</v>
       </c>
       <c r="L26" s="127">
         <f t="shared" si="3"/>
-        <v>34528.297562540021</v>
+        <v>26618.300106800001</v>
       </c>
       <c r="M26" s="107">
         <f t="shared" si="4"/>
-        <v>162.60000000000036</v>
+        <v>351.79999999999927</v>
       </c>
       <c r="N26" s="104">
         <f>J26+L26</f>
-        <v>49778.063762540056</v>
+        <v>59612.566706799938</v>
       </c>
       <c r="O26" s="97">
         <f>N26+'prorrateo '!M19</f>
-        <v>248853.08830308012</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>284810.77513159986</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="98">
         <v>19</v>
       </c>
       <c r="B27" s="90">
         <v>19</v>
       </c>
-      <c r="C27" s="196" t="s">
+      <c r="C27" s="195" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="197"/>
-      <c r="E27" s="198">
+      <c r="D27" s="196"/>
+      <c r="E27" s="197">
         <v>1.08</v>
       </c>
       <c r="F27" s="188"/>
-      <c r="G27" s="189"/>
-      <c r="H27" s="190">
+      <c r="G27" s="188"/>
+      <c r="H27" s="189">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="191">
+      <c r="I27" s="190">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="192"/>
-      <c r="K27" s="193"/>
-      <c r="L27" s="194">
+      <c r="J27" s="191"/>
+      <c r="K27" s="192"/>
+      <c r="L27" s="193">
         <f t="shared" si="3"/>
-        <v>5039.2650496680035</v>
-      </c>
-      <c r="M27" s="195">
-        <v>0</v>
-      </c>
-      <c r="N27" s="190">
+        <v>3884.8329885600006</v>
+      </c>
+      <c r="M27" s="194">
+        <v>0</v>
+      </c>
+      <c r="N27" s="189">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="O27" s="97">
         <f>N27+'prorrateo '!M20</f>
-        <v>31867.81626693601</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>31936.219092719999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="98">
         <v>20</v>
       </c>
@@ -5196,21 +5219,21 @@
       <c r="K28" s="106"/>
       <c r="L28" s="127">
         <f t="shared" si="3"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="M28" s="107">
         <v>0</v>
       </c>
       <c r="N28" s="104">
         <f t="shared" si="6"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="O28" s="97">
         <f>N28+'prorrateo '!M21</f>
-        <v>31867.81626693601</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>31936.219092719999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="98"/>
       <c r="B29" s="90"/>
       <c r="C29" s="158" t="s">
@@ -5228,21 +5251,21 @@
       <c r="K29" s="148"/>
       <c r="L29" s="149">
         <f t="shared" si="3"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="M29" s="150">
         <v>0</v>
       </c>
       <c r="N29" s="147">
         <f t="shared" si="6"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="O29" s="97">
         <f>N29+'prorrateo '!M22</f>
-        <v>304970.27188399207</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>342576.70908873709</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="98"/>
       <c r="B30" s="90"/>
       <c r="C30" s="169" t="s">
@@ -5260,21 +5283,21 @@
       <c r="K30" s="106"/>
       <c r="L30" s="127">
         <f t="shared" si="3"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="M30" s="107">
         <v>0</v>
       </c>
       <c r="N30" s="104">
         <f t="shared" si="6"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="O30" s="97">
         <f>N30+'prorrateo '!M23</f>
-        <v>31867.81626693601</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>31936.219092719999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="98"/>
       <c r="B31" s="90"/>
       <c r="C31" s="169" t="s">
@@ -5294,55 +5317,55 @@
       <c r="K31" s="106"/>
       <c r="L31" s="127">
         <f t="shared" si="3"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="M31" s="107">
         <v>0</v>
       </c>
       <c r="N31" s="104">
         <f t="shared" si="6"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="O31" s="97">
         <f>N31+'prorrateo '!M24</f>
-        <v>31867.81626693601</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>31936.219092719999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="99"/>
-      <c r="B32" s="215"/>
-      <c r="C32" s="158" t="s">
+      <c r="B32" s="208"/>
+      <c r="C32" s="169" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="146" t="s">
+      <c r="D32" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="146">
+      <c r="E32" s="102">
         <v>1.08</v>
       </c>
-      <c r="F32" s="146"/>
-      <c r="G32" s="146"/>
-      <c r="H32" s="147"/>
-      <c r="I32" s="159"/>
-      <c r="J32" s="160"/>
-      <c r="K32" s="148"/>
-      <c r="L32" s="149">
+      <c r="F32" s="102"/>
+      <c r="G32" s="102"/>
+      <c r="H32" s="104"/>
+      <c r="I32" s="170"/>
+      <c r="J32" s="171"/>
+      <c r="K32" s="106"/>
+      <c r="L32" s="127">
         <f t="shared" si="3"/>
-        <v>5039.2650496680035</v>
-      </c>
-      <c r="M32" s="150">
-        <v>0</v>
-      </c>
-      <c r="N32" s="147">
+        <v>3884.8329885600006</v>
+      </c>
+      <c r="M32" s="107">
+        <v>0</v>
+      </c>
+      <c r="N32" s="104">
         <f t="shared" si="6"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="O32" s="97">
         <f>N32+'prorrateo '!M25</f>
-        <v>31867.81626693601</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+        <v>31936.219092719999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="98"/>
       <c r="B33" s="90"/>
       <c r="C33" s="130" t="s">
@@ -5362,21 +5385,21 @@
       <c r="K33" s="113"/>
       <c r="L33" s="127">
         <f t="shared" si="3"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="M33" s="107">
         <v>0</v>
       </c>
       <c r="N33" s="104">
         <f t="shared" si="6"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="O33" s="97">
         <f>N33+'prorrateo '!M26</f>
-        <v>31867.81626693601</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+        <v>31936.219092719999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="98"/>
       <c r="B34" s="90"/>
       <c r="C34" s="130" t="s">
@@ -5396,21 +5419,21 @@
       <c r="K34" s="113"/>
       <c r="L34" s="127">
         <f t="shared" si="3"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="M34" s="107">
         <v>0</v>
       </c>
       <c r="N34" s="104">
         <f t="shared" si="6"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="O34" s="97">
         <f>N34+'prorrateo '!M27</f>
-        <v>31867.81626693601</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+        <v>31936.219092719999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="98">
         <v>21</v>
       </c>
@@ -5435,21 +5458,21 @@
       <c r="K35" s="106"/>
       <c r="L35" s="127">
         <f t="shared" si="3"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="M35" s="107">
         <v>0</v>
       </c>
       <c r="N35" s="104">
         <f t="shared" si="6"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="O35" s="97">
         <f>N35+'prorrateo '!M28</f>
-        <v>31867.81626693601</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+        <v>31936.219092719999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="98">
         <v>22</v>
       </c>
@@ -5476,21 +5499,21 @@
       <c r="K36" s="106"/>
       <c r="L36" s="127">
         <f t="shared" si="3"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="M36" s="107">
         <v>0</v>
       </c>
       <c r="N36" s="104">
         <f t="shared" si="6"/>
-        <v>5039.2650496680035</v>
+        <v>3884.8329885600006</v>
       </c>
       <c r="O36" s="97">
         <f>N36+'prorrateo '!M29</f>
-        <v>31867.81626693601</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+        <v>58550.155246998736</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="98">
         <v>23</v>
       </c>
@@ -5520,7 +5543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="98">
         <v>24</v>
       </c>
@@ -5534,21 +5557,21 @@
       <c r="I38" s="112"/>
       <c r="J38" s="117">
         <f>SUM(J10:J37)</f>
-        <v>199922.9342899998</v>
+        <v>306814.79180000001</v>
       </c>
       <c r="K38" s="113"/>
       <c r="L38" s="113">
         <f>SUM(L10:L37)</f>
-        <v>466598.61571000051</v>
+        <v>359706.75820000027</v>
       </c>
       <c r="M38" s="114"/>
       <c r="N38" s="110">
         <f>SUM(N10:N37)</f>
-        <v>666521.55000000028</v>
+        <v>666521.54999999958</v>
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78"/>
       <c r="C39" s="91"/>
       <c r="D39" s="92"/>
@@ -5561,7 +5584,7 @@
       <c r="H39" s="93"/>
       <c r="I39" s="94">
         <f>SUM(I10:I38)</f>
-        <v>149.21689999999987</v>
+        <v>228.99799999999999</v>
       </c>
       <c r="J39" s="126"/>
       <c r="K39" s="94"/>
@@ -5573,41 +5596,41 @@
       <c r="N39" s="93"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="236"/>
-      <c r="D40" s="234"/>
-      <c r="E40" s="234"/>
-      <c r="F40" s="234"/>
-      <c r="G40" s="234"/>
-      <c r="H40" s="234"/>
-      <c r="I40" s="234"/>
-      <c r="J40" s="234"/>
-      <c r="K40" s="234"/>
-      <c r="L40" s="234"/>
-      <c r="M40" s="234"/>
-      <c r="N40" s="234"/>
+      <c r="C40" s="229"/>
+      <c r="D40" s="227"/>
+      <c r="E40" s="227"/>
+      <c r="F40" s="227"/>
+      <c r="G40" s="227"/>
+      <c r="H40" s="227"/>
+      <c r="I40" s="227"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="227"/>
+      <c r="L40" s="227"/>
+      <c r="M40" s="227"/>
+      <c r="N40" s="227"/>
       <c r="O40" s="95"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H41" s="79"/>
       <c r="J41" s="96"/>
       <c r="K41" s="96"/>
       <c r="L41" s="96"/>
       <c r="N41" s="97"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L44" s="151"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="96"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E46" s="152"/>
       <c r="F46" s="152"/>
       <c r="G46" s="152"/>

--- a/ROSALES/Diciembre/expensas rosales Diciembre.xlsx
+++ b/ROSALES/Diciembre/expensas rosales Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9A7BE8-978E-49F6-BA85-448C78A78EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CF5349-D202-45F7-95AB-61BE43B2E611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$68</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="127">
   <si>
     <t>TOTAL</t>
   </si>
@@ -348,10 +348,6 @@
   </si>
   <si>
     <t>Anabella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAJA NO REAL, YA QUE DE ESTE FONDO SE PAGA EDESUR DE LAS UNIDADES
-</t>
   </si>
   <si>
     <t>ARBA</t>
@@ -407,6 +403,20 @@
   </si>
   <si>
     <t>CUOTA PLAN DE PAGOS (5/6)</t>
+  </si>
+  <si>
+    <t>RECUPERO DE DEUDORES DE EDESUR  HISTORICOS - LEER CARTEL VERDE</t>
+  </si>
+  <si>
+    <t>Estimados, buenos días / buenas tardes,
+A partir de las expensas emitidas desde diciembre de 2025, el consumo y pago de EDESUR deja de contabilizarse por separado y pasa a estar incluido dentro de los gastos ordinarios mensuales.
+De esta manera, el consorcio pasa a manejar una única caja, donde se reflejan todos los ingresos y egresos (EDESUR, seguros, AYSA, mantenimiento, sueldos, TSG, etc.), logrando mayor claridad y control.
+Desde ahora:
+ • El monto correspondiente a EDESUR figurará en el prorrateo de cada unidad.
+ • Estará incluido en el total a pagar.
+ • El pago mensual de EDESUR se verá reflejado dentro de la caja general de expensas.
+Esta unificación evita desbalances y cruces de fondos que se daban anteriormente.
+Quedamos a disposición por cualquier consulta.</t>
   </si>
 </sst>
 </file>
@@ -1368,58 +1378,60 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1837,17 +1849,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:F69"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1855,207 +1867,207 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
         <v>105</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="213">
+      <c r="C18" s="33">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="215">
+      <c r="C19" s="234">
         <v>330057.21999999997</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="28" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="213">
+      <c r="C20" s="33">
         <v>85000</v>
       </c>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="213">
+      <c r="C21" s="33">
         <v>15748</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6"/>
       <c r="F21" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="28" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="213">
+      <c r="C22" s="33">
         <v>83400</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="40"/>
       <c r="B23" s="41"/>
-      <c r="C23" s="212">
+      <c r="C23" s="23">
         <f>SUM(C17:C22)</f>
         <v>590859.22</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="35" t="s">
         <v>12</v>
       </c>
       <c r="B24" s="39"/>
-      <c r="C24" s="36"/>
+      <c r="C24" s="235"/>
       <c r="D24" s="45"/>
       <c r="F24" s="12"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="28" t="s">
         <v>97</v>
       </c>
       <c r="B25" s="42"/>
-      <c r="C25" s="213">
+      <c r="C25" s="33">
         <f>349151.87+ (349151.87*10%)</f>
         <v>384067.05699999997</v>
       </c>
       <c r="D25" s="45"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B26" s="42"/>
-      <c r="C26" s="213">
+      <c r="C26" s="33">
         <v>192033.53</v>
       </c>
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="28" t="s">
         <v>98</v>
       </c>
       <c r="B27" s="42"/>
-      <c r="C27" s="213">
+      <c r="C27" s="33">
         <v>5684</v>
       </c>
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B28" s="42"/>
-      <c r="C28" s="213">
+      <c r="C28" s="33">
         <v>10000</v>
       </c>
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B29" s="42"/>
-      <c r="C29" s="213">
+      <c r="C29" s="33">
         <v>55000</v>
       </c>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="28" t="s">
         <v>91</v>
       </c>
@@ -2065,7 +2077,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="40"/>
       <c r="B31" s="41"/>
       <c r="C31" s="23">
@@ -2074,7 +2086,7 @@
       </c>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="30" t="s">
         <v>6</v>
       </c>
@@ -2085,42 +2097,42 @@
       </c>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C33" s="24"/>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="28"/>
       <c r="B35" s="28"/>
       <c r="C35" s="211"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="28"/>
       <c r="B36" s="28"/>
       <c r="C36" s="211"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
       <c r="C37" s="34"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C38" s="25"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="173" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B39" s="173"/>
       <c r="C39" s="174">
@@ -2128,11 +2140,11 @@
       </c>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C40" s="25"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>15</v>
       </c>
@@ -2143,7 +2155,7 @@
       </c>
       <c r="E41" s="6"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="18" t="s">
         <v>7</v>
       </c>
@@ -2153,37 +2165,37 @@
         <v>1237643.807</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="220" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="B45" s="221"/>
       <c r="C45" s="221"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="221"/>
       <c r="B46" s="221"/>
       <c r="C46" s="221"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="221"/>
       <c r="B47" s="221"/>
       <c r="C47" s="221"/>
     </row>
-    <row r="48" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="221"/>
       <c r="B48" s="221"/>
       <c r="C48" s="221"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
     </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="C49" s="154"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="200" t="s">
         <v>100</v>
       </c>
@@ -2194,19 +2206,19 @@
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="200" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B51" s="28"/>
-      <c r="C51" s="31">
+      <c r="C51" s="231">
         <f>-(C43-C30)</f>
         <v>-1237643.807</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="200" t="s">
         <v>96</v>
       </c>
@@ -2216,124 +2228,133 @@
         <v>2466028.3590707099</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="200" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B53" s="28"/>
-      <c r="C53" s="235">
+      <c r="C53" s="217">
         <f>-Edesur!C7</f>
         <v>-666521.55000000005</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="200" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B54" s="28"/>
       <c r="C54" s="31">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="200" t="s">
         <v>125</v>
       </c>
       <c r="B55" s="28"/>
-      <c r="C55" s="202">
+      <c r="C55" s="31">
+        <v>-1767562.94</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="200" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="28"/>
+      <c r="C56" s="202">
         <v>107386.2</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="200" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="200" t="s">
         <v>8</v>
       </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="201">
-        <f>SUM(C50:C55)</f>
-        <v>1806679.26359171</v>
-      </c>
-      <c r="D56" s="5"/>
-    </row>
-    <row r="57" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="9"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="10"/>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="216"/>
-      <c r="B58" s="216"/>
-      <c r="C58" s="216"/>
-      <c r="F58" s="44"/>
-    </row>
-    <row r="59" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="217"/>
-      <c r="B59" s="217"/>
-      <c r="C59" s="217"/>
-    </row>
-    <row r="60" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="26" t="s">
+      <c r="B57" s="28"/>
+      <c r="C57" s="201">
+        <f>SUM(C50:C56)</f>
+        <v>39116.323591710112</v>
+      </c>
+      <c r="D57" s="5"/>
+    </row>
+    <row r="58" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="9"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="10"/>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="218"/>
+      <c r="B59" s="218"/>
+      <c r="C59" s="218"/>
+      <c r="F59" s="44"/>
+    </row>
+    <row r="60" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="219"/>
+      <c r="B60" s="219"/>
+      <c r="C60" s="219"/>
+    </row>
+    <row r="61" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B60" s="27"/>
-      <c r="C60" s="29"/>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="28" t="s">
+      <c r="B61" s="27"/>
+      <c r="C61" s="29"/>
+    </row>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="31">
+      <c r="B62" s="28"/>
+      <c r="C62" s="31">
         <f>-C41</f>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="28"/>
-      <c r="B62" s="28"/>
-      <c r="C62" s="31"/>
-    </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="28"/>
       <c r="B63" s="28"/>
-      <c r="C63" s="32"/>
-    </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="155" t="s">
-        <v>0</v>
-      </c>
-      <c r="B64" s="156"/>
-      <c r="C64" s="157">
-        <f>SUM(C60:C63)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="218" t="s">
-        <v>107</v>
-      </c>
-      <c r="B65" s="219"/>
-      <c r="C65" s="219"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="219"/>
-      <c r="B66" s="219"/>
-      <c r="C66" s="219"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="219"/>
-      <c r="B67" s="219"/>
-      <c r="C67" s="219"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
+      <c r="C63" s="31"/>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="28"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="32"/>
+    </row>
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="155" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="156"/>
+      <c r="C65" s="157">
+        <f>SUM(C61:C64)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="232" t="s">
+        <v>108</v>
+      </c>
+      <c r="B66" s="233"/>
+      <c r="C66" s="233"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="233"/>
+      <c r="B67" s="233"/>
+      <c r="C67" s="233"/>
+    </row>
+    <row r="68" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="233"/>
+      <c r="B68" s="233"/>
+      <c r="C68" s="233"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A58:C59"/>
-    <mergeCell ref="A65:C67"/>
+    <mergeCell ref="A59:C60"/>
+    <mergeCell ref="A66:C68"/>
     <mergeCell ref="A45:C48"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
@@ -2353,26 +2374,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" customWidth="1"/>
-    <col min="9" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="9" max="10" width="10.6640625" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="11" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>103</v>
       </c>
@@ -2390,7 +2411,7 @@
       <c r="G1" s="224"/>
       <c r="H1" s="224"/>
       <c r="I1" s="225" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J1" s="225"/>
       <c r="K1" s="225"/>
@@ -2402,7 +2423,7 @@
         <v>1237643.807</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
@@ -2431,22 +2452,22 @@
         <v>104</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K2" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L2" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M2" s="51" t="s">
         <v>30</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2462,7 +2483,7 @@
       <c r="E3" s="129">
         <v>134104.34113548099</v>
       </c>
-      <c r="F3" s="232">
+      <c r="F3" s="214">
         <f>E3</f>
         <v>134104.34113548099</v>
       </c>
@@ -2500,7 +2521,7 @@
         <v>114343.59853770002</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2516,7 +2537,7 @@
       <c r="E4" s="129">
         <v>130106.86867093903</v>
       </c>
-      <c r="F4" s="232">
+      <c r="F4" s="214">
         <f>E4</f>
         <v>130106.86867093903</v>
       </c>
@@ -2554,7 +2575,7 @@
         <v>113896.06977629999</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2568,7 +2589,7 @@
       <c r="E5" s="129">
         <v>160726.72885904807</v>
       </c>
-      <c r="F5" s="232">
+      <c r="F5" s="214">
         <f>160000-F23</f>
         <v>134409.67677473198</v>
       </c>
@@ -2606,7 +2627,7 @@
         <v>140146.98204048874</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="62" t="s">
         <v>37</v>
       </c>
@@ -2620,7 +2641,7 @@
       <c r="E6" s="129">
         <v>242855.68957555902</v>
       </c>
-      <c r="F6" s="232">
+      <c r="F6" s="214">
         <f>E6</f>
         <v>242855.68957555902</v>
       </c>
@@ -2648,7 +2669,7 @@
         <f t="shared" si="4"/>
         <v>52100</v>
       </c>
-      <c r="M6" s="231">
+      <c r="M6" s="213">
         <f t="shared" si="5"/>
         <v>151256.37574692001</v>
       </c>
@@ -2658,7 +2679,7 @@
       </c>
       <c r="P6" s="175"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
@@ -2674,7 +2695,7 @@
       <c r="E7" s="129">
         <v>130486.97654548101</v>
       </c>
-      <c r="F7" s="232">
+      <c r="F7" s="214">
         <f t="shared" ref="F7:F11" si="7">E7</f>
         <v>130486.97654548101</v>
       </c>
@@ -2712,7 +2733,7 @@
       </c>
       <c r="P7" s="175"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="58" t="s">
         <v>40</v>
       </c>
@@ -2726,7 +2747,7 @@
       <c r="E8" s="129">
         <v>128193.61387093902</v>
       </c>
-      <c r="F8" s="232">
+      <c r="F8" s="214">
         <f t="shared" si="7"/>
         <v>128193.61387093902</v>
       </c>
@@ -2763,7 +2784,7 @@
         <v>113896.06977629999</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>42</v>
       </c>
@@ -2777,7 +2798,7 @@
       <c r="E9" s="129">
         <v>129633.514845481</v>
       </c>
-      <c r="F9" s="232">
+      <c r="F9" s="214">
         <f>130000</f>
         <v>130000</v>
       </c>
@@ -2815,7 +2836,7 @@
       </c>
       <c r="P9" s="175"/>
     </row>
-    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="177" t="s">
         <v>44</v>
       </c>
@@ -2831,7 +2852,7 @@
       <c r="E10" s="181">
         <v>122885.26967093899</v>
       </c>
-      <c r="F10" s="233">
+      <c r="F10" s="215">
         <f t="shared" si="7"/>
         <v>122885.26967093899</v>
       </c>
@@ -2865,7 +2886,7 @@
         <v>113896.06977629999</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -2879,7 +2900,7 @@
       <c r="E11" s="129">
         <v>127318.37378458401</v>
       </c>
-      <c r="F11" s="232">
+      <c r="F11" s="214">
         <f t="shared" si="7"/>
         <v>127318.37378458401</v>
       </c>
@@ -2916,7 +2937,7 @@
         <v>112777.2478728</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="58" t="s">
         <v>47</v>
       </c>
@@ -2930,7 +2951,7 @@
       <c r="E12" s="129">
         <v>144392.25191819097</v>
       </c>
-      <c r="F12" s="232">
+      <c r="F12" s="214">
         <f t="shared" ref="F12" si="8">E12</f>
         <v>144392.25191819097</v>
       </c>
@@ -2967,7 +2988,7 @@
         <v>116581.2423447</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>49</v>
       </c>
@@ -2983,7 +3004,7 @@
       <c r="E13" s="129">
         <v>175045.18024548097</v>
       </c>
-      <c r="F13" s="232">
+      <c r="F13" s="214">
         <f>E13</f>
         <v>175045.18024548097</v>
       </c>
@@ -3021,7 +3042,7 @@
         <v>114343.59853770002</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="62" t="s">
         <v>49</v>
       </c>
@@ -3037,7 +3058,7 @@
       <c r="E14" s="129">
         <v>83972.551670038971</v>
       </c>
-      <c r="F14" s="232">
+      <c r="F14" s="214">
         <f>109600-F25</f>
         <v>84009.676774731997</v>
       </c>
@@ -3074,7 +3095,7 @@
         <v>113858.94467160697</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>53</v>
       </c>
@@ -3090,7 +3111,7 @@
       <c r="E15" s="129">
         <v>124636.07021507998</v>
       </c>
-      <c r="F15" s="232"/>
+      <c r="F15" s="214"/>
       <c r="G15" s="56">
         <f t="shared" si="0"/>
         <v>124636.07021507998</v>
@@ -3124,7 +3145,7 @@
         <v>242398.76089648317</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="58" t="s">
         <v>56</v>
       </c>
@@ -3140,7 +3161,7 @@
       <c r="E16" s="129">
         <v>134085.060618191</v>
       </c>
-      <c r="F16" s="232">
+      <c r="F16" s="214">
         <f t="shared" ref="F16:F21" si="9">E16</f>
         <v>134085.060618191</v>
       </c>
@@ -3178,7 +3199,7 @@
         <v>116581.2423447</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>59</v>
       </c>
@@ -3192,7 +3213,7 @@
       <c r="E17" s="129">
         <v>121859.97038458401</v>
       </c>
-      <c r="F17" s="232">
+      <c r="F17" s="214">
         <f t="shared" si="9"/>
         <v>121859.97038458401</v>
       </c>
@@ -3229,7 +3250,7 @@
         <v>112777.24787279998</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="204" t="s">
         <v>61</v>
       </c>
@@ -3243,7 +3264,7 @@
       <c r="E18" s="129">
         <v>130961.95351819103</v>
       </c>
-      <c r="F18" s="232">
+      <c r="F18" s="214">
         <f t="shared" si="9"/>
         <v>130961.95351819103</v>
       </c>
@@ -3283,7 +3304,7 @@
       <c r="P18" s="206"/>
       <c r="Q18" s="203"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="62" t="s">
         <v>63</v>
       </c>
@@ -3297,7 +3318,7 @@
       <c r="E19" s="129">
         <v>190590.86978054006</v>
       </c>
-      <c r="F19" s="232">
+      <c r="F19" s="214">
         <f t="shared" si="9"/>
         <v>190590.86978054006</v>
       </c>
@@ -3334,7 +3355,7 @@
         <v>165585.641718</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="24" x14ac:dyDescent="0.3">
       <c r="A20" s="184"/>
       <c r="B20" s="178" t="s">
         <v>99</v>
@@ -3348,7 +3369,7 @@
       <c r="E20" s="181">
         <v>25590.323225268006</v>
       </c>
-      <c r="F20" s="233">
+      <c r="F20" s="215">
         <f t="shared" si="9"/>
         <v>25590.323225268006</v>
       </c>
@@ -3382,7 +3403,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>57</v>
@@ -3396,7 +3417,7 @@
       <c r="E21" s="129">
         <v>25590.323225268006</v>
       </c>
-      <c r="F21" s="232">
+      <c r="F21" s="214">
         <f t="shared" si="9"/>
         <v>25590.323225268006</v>
       </c>
@@ -3433,7 +3454,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="139"/>
       <c r="B22" s="140"/>
       <c r="C22" s="141" t="s">
@@ -3445,7 +3466,7 @@
       <c r="E22" s="143">
         <v>298692.77884232404</v>
       </c>
-      <c r="F22" s="234">
+      <c r="F22" s="216">
         <v>0</v>
       </c>
       <c r="G22" s="144">
@@ -3481,7 +3502,7 @@
         <v>334807.04311161704</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>35</v>
       </c>
@@ -3495,7 +3516,7 @@
       <c r="E23" s="129">
         <v>25590.323225268006</v>
       </c>
-      <c r="F23" s="232">
+      <c r="F23" s="214">
         <f>E23</f>
         <v>25590.323225268006</v>
       </c>
@@ -3532,7 +3553,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="58" t="s">
         <v>49</v>
       </c>
@@ -3548,7 +3569,7 @@
       <c r="E24" s="129">
         <v>25590.323225268006</v>
       </c>
-      <c r="F24" s="232">
+      <c r="F24" s="214">
         <f t="shared" ref="F24" si="10">E24</f>
         <v>25590.323225268006</v>
       </c>
@@ -3585,7 +3606,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -3601,7 +3622,7 @@
       <c r="E25" s="129">
         <v>25590.323225268006</v>
       </c>
-      <c r="F25" s="232">
+      <c r="F25" s="214">
         <f>E25</f>
         <v>25590.323225268006</v>
       </c>
@@ -3638,7 +3659,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="58" t="s">
         <v>63</v>
       </c>
@@ -3652,7 +3673,7 @@
       <c r="E26" s="129">
         <v>25590.323225268006</v>
       </c>
-      <c r="F26" s="232">
+      <c r="F26" s="214">
         <f t="shared" ref="F26:F28" si="11">E26</f>
         <v>25590.323225268006</v>
       </c>
@@ -3689,7 +3710,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="58" t="s">
         <v>63</v>
       </c>
@@ -3703,7 +3724,7 @@
       <c r="E27" s="129">
         <v>25590.323225268006</v>
       </c>
-      <c r="F27" s="232">
+      <c r="F27" s="214">
         <f t="shared" si="11"/>
         <v>25590.323225268006</v>
       </c>
@@ -3744,7 +3765,7 @@
         <v>241771.51623107606</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="66"/>
       <c r="B28" s="65" t="str">
         <f>B7</f>
@@ -3759,7 +3780,7 @@
       <c r="E28" s="129">
         <v>25590.323225268006</v>
       </c>
-      <c r="F28" s="232">
+      <c r="F28" s="214">
         <f t="shared" si="11"/>
         <v>25590.323225268006</v>
       </c>
@@ -3796,7 +3817,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="66" t="s">
         <v>53</v>
       </c>
@@ -3846,7 +3867,7 @@
         <v>50780.48926987873</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="68"/>
@@ -3861,7 +3882,7 @@
       <c r="L30" s="71"/>
       <c r="M30" s="71"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="72"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74" t="s">
@@ -3893,12 +3914,12 @@
         <v>3398007.4200824555</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K32" s="22"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="223" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B33" s="223"/>
       <c r="C33" s="223"/>
@@ -3913,7 +3934,7 @@
       <c r="L33" s="223"/>
       <c r="M33" s="223"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="223"/>
       <c r="B34" s="223"/>
       <c r="C34" s="223"/>
@@ -3928,7 +3949,7 @@
       <c r="L34" s="223"/>
       <c r="M34" s="223"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="223"/>
       <c r="B35" s="223"/>
       <c r="C35" s="223"/>
@@ -3943,7 +3964,7 @@
       <c r="L35" s="223"/>
       <c r="M35" s="223"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="223"/>
       <c r="B36" s="223"/>
       <c r="C36" s="223"/>
@@ -3958,7 +3979,7 @@
       <c r="L36" s="223"/>
       <c r="M36" s="223"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -3978,26 +3999,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="226" t="s">
         <v>77</v>
       </c>
@@ -4016,7 +4037,7 @@
       <c r="N1" s="228"/>
       <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
       <c r="C2" s="161"/>
@@ -4034,7 +4055,7 @@
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
       <c r="C3" s="163"/>
@@ -4052,7 +4073,7 @@
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
       <c r="C4" s="163"/>
@@ -4072,7 +4093,7 @@
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
       <c r="C5" s="163"/>
@@ -4090,7 +4111,7 @@
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
       <c r="C6" s="209" t="str">
@@ -4111,12 +4132,12 @@
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="81"/>
       <c r="B7" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="214">
+      <c r="C7" s="212">
         <v>666521.55000000005</v>
       </c>
       <c r="D7" s="28"/>
@@ -4138,7 +4159,7 @@
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="81"/>
       <c r="B8" s="80" t="s">
         <v>77</v>
@@ -4163,7 +4184,7 @@
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="87" t="s">
         <v>78</v>
       </c>
@@ -4208,7 +4229,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="98">
         <v>1</v>
       </c>
@@ -4264,7 +4285,7 @@
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="99">
         <v>2</v>
       </c>
@@ -4320,7 +4341,7 @@
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="98">
         <v>3</v>
       </c>
@@ -4379,7 +4400,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="98">
         <v>4</v>
       </c>
@@ -4435,7 +4456,7 @@
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="98">
         <v>6</v>
       </c>
@@ -4491,7 +4512,7 @@
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="98">
         <v>7</v>
       </c>
@@ -4546,7 +4567,7 @@
         <v>193262.33236106002</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="98">
         <v>8</v>
       </c>
@@ -4601,7 +4622,7 @@
         <v>176418.02467122104</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="98">
         <v>9</v>
       </c>
@@ -4656,7 +4677,7 @@
         <v>156160.19516105996</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="98">
         <v>10</v>
       </c>
@@ -4711,7 +4732,7 @@
         <v>173495.33869936003</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="98">
         <v>11</v>
       </c>
@@ -4766,7 +4787,7 @@
         <v>217631.51514914012</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="98">
         <v>12</v>
       </c>
@@ -4821,7 +4842,7 @@
         <v>210060.13742574007</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="98">
         <v>13</v>
       </c>
@@ -4876,7 +4897,7 @@
         <v>164132.47985636702</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="98">
         <v>14</v>
       </c>
@@ -4931,7 +4952,7 @@
         <v>316415.8483230432</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="98">
         <v>15</v>
       </c>
@@ -4986,7 +5007,7 @@
         <v>202062.87314913995</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="98">
         <v>16</v>
       </c>
@@ -5041,7 +5062,7 @@
         <v>157439.00429935998</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="98">
         <v>17</v>
       </c>
@@ -5097,7 +5118,7 @@
         <v>169068.60654914001</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="98">
         <v>18</v>
       </c>
@@ -5152,7 +5173,7 @@
         <v>284810.77513159986</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="98">
         <v>19</v>
       </c>
@@ -5194,7 +5215,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="98">
         <v>20</v>
       </c>
@@ -5233,7 +5254,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="98"/>
       <c r="B29" s="90"/>
       <c r="C29" s="158" t="s">
@@ -5265,7 +5286,7 @@
         <v>342576.70908873709</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="98"/>
       <c r="B30" s="90"/>
       <c r="C30" s="169" t="s">
@@ -5297,7 +5318,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="98"/>
       <c r="B31" s="90"/>
       <c r="C31" s="169" t="s">
@@ -5331,7 +5352,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="99"/>
       <c r="B32" s="208"/>
       <c r="C32" s="169" t="s">
@@ -5365,7 +5386,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="98"/>
       <c r="B33" s="90"/>
       <c r="C33" s="130" t="s">
@@ -5399,7 +5420,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="98"/>
       <c r="B34" s="90"/>
       <c r="C34" s="130" t="s">
@@ -5433,7 +5454,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="98">
         <v>21</v>
       </c>
@@ -5472,7 +5493,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="98">
         <v>22</v>
       </c>
@@ -5513,7 +5534,7 @@
         <v>58550.155246998736</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="98">
         <v>23</v>
       </c>
@@ -5543,7 +5564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="98">
         <v>24</v>
       </c>
@@ -5571,7 +5592,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="78"/>
       <c r="C39" s="91"/>
       <c r="D39" s="92"/>
@@ -5596,7 +5617,7 @@
       <c r="N39" s="93"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="95" t="s">
         <v>88</v>
       </c>
@@ -5614,23 +5635,23 @@
       <c r="N40" s="227"/>
       <c r="O40" s="95"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="H41" s="79"/>
       <c r="J41" s="96"/>
       <c r="K41" s="96"/>
       <c r="L41" s="96"/>
       <c r="N41" s="97"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L44" s="151"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L45" s="96"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E46" s="152"/>
       <c r="F46" s="152"/>
       <c r="G46" s="152"/>

--- a/ROSALES/Diciembre/expensas rosales Diciembre.xlsx
+++ b/ROSALES/Diciembre/expensas rosales Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CF5349-D202-45F7-95AB-61BE43B2E611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C7EC58-4A5B-4AFE-A31D-75DCE9355A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -1384,6 +1384,13 @@
     <xf numFmtId="44" fontId="20" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1419,18 +1426,11 @@
     <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1850,16 +1850,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1867,22 +1867,22 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
@@ -1893,51 +1893,51 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>105</v>
       </c>
@@ -1948,18 +1948,18 @@
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="234">
+      <c r="C19" s="219">
         <v>330057.21999999997</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>25</v>
       </c>
@@ -1970,7 +1970,7 @@
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
         <v>120</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
         <v>11</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>83400</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="40"/>
       <c r="B23" s="41"/>
       <c r="C23" s="23">
@@ -2003,16 +2003,16 @@
         <v>590859.22</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
         <v>12</v>
       </c>
       <c r="B24" s="39"/>
-      <c r="C24" s="235"/>
+      <c r="C24" s="220"/>
       <c r="D24" s="45"/>
       <c r="F24" s="12"/>
     </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
         <v>97</v>
       </c>
@@ -2024,7 +2024,7 @@
       <c r="D25" s="45"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
         <v>121</v>
       </c>
@@ -2035,7 +2035,7 @@
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
         <v>98</v>
       </c>
@@ -2046,7 +2046,7 @@
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
         <v>122</v>
       </c>
@@ -2057,7 +2057,7 @@
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
         <v>110</v>
       </c>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
         <v>91</v>
       </c>
@@ -2077,7 +2077,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="40"/>
       <c r="B31" s="41"/>
       <c r="C31" s="23">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="30" t="s">
         <v>6</v>
       </c>
@@ -2097,40 +2097,40 @@
       </c>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C33" s="24"/>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="28"/>
       <c r="B35" s="28"/>
       <c r="C35" s="211"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="28"/>
       <c r="B36" s="28"/>
       <c r="C36" s="211"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
       <c r="C37" s="34"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C38" s="25"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="173" t="s">
         <v>123</v>
       </c>
@@ -2140,11 +2140,11 @@
       </c>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C40" s="25"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>15</v>
       </c>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="E41" s="6"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="18" t="s">
         <v>7</v>
       </c>
@@ -2165,37 +2165,37 @@
         <v>1237643.807</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="220" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="223" t="s">
         <v>126</v>
       </c>
-      <c r="B45" s="221"/>
-      <c r="C45" s="221"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="221"/>
-      <c r="B46" s="221"/>
-      <c r="C46" s="221"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="221"/>
-      <c r="B47" s="221"/>
-      <c r="C47" s="221"/>
-    </row>
-    <row r="48" spans="1:6" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="221"/>
-      <c r="B48" s="221"/>
-      <c r="C48" s="221"/>
+      <c r="B45" s="224"/>
+      <c r="C45" s="224"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="224"/>
+      <c r="B46" s="224"/>
+      <c r="C46" s="224"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="224"/>
+      <c r="B47" s="224"/>
+      <c r="C47" s="224"/>
+    </row>
+    <row r="48" spans="1:6" ht="133.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="224"/>
+      <c r="B48" s="224"/>
+      <c r="C48" s="224"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
     </row>
-    <row r="49" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="C49" s="154"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>100</v>
       </c>
@@ -2206,19 +2206,19 @@
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="200" t="s">
         <v>119</v>
       </c>
       <c r="B51" s="28"/>
-      <c r="C51" s="231">
+      <c r="C51" s="218">
         <f>-(C43-C30)</f>
         <v>-1237643.807</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="200" t="s">
         <v>96</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>2466028.3590707099</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="200" t="s">
         <v>115</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>-666521.55000000005</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="200" t="s">
         <v>114</v>
       </c>
@@ -2247,16 +2247,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="200" t="s">
         <v>125</v>
       </c>
       <c r="B55" s="28"/>
-      <c r="C55" s="31">
+      <c r="C55" s="218">
         <v>-1767562.94</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="200" t="s">
         <v>124</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>107386.2</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="200" t="s">
         <v>8</v>
       </c>
@@ -2276,30 +2276,30 @@
       </c>
       <c r="D57" s="5"/>
     </row>
-    <row r="58" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9"/>
       <c r="B58" s="8"/>
       <c r="C58" s="10"/>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="218"/>
-      <c r="B59" s="218"/>
-      <c r="C59" s="218"/>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="221"/>
+      <c r="B59" s="221"/>
+      <c r="C59" s="221"/>
       <c r="F59" s="44"/>
     </row>
-    <row r="60" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="219"/>
-      <c r="B60" s="219"/>
-      <c r="C60" s="219"/>
-    </row>
-    <row r="61" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="222"/>
+      <c r="B60" s="222"/>
+      <c r="C60" s="222"/>
+    </row>
+    <row r="61" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
         <v>20</v>
       </c>
       <c r="B61" s="27"/>
       <c r="C61" s="29"/>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="28" t="s">
         <v>23</v>
       </c>
@@ -2309,17 +2309,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="28"/>
       <c r="B63" s="28"/>
       <c r="C63" s="31"/>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="28"/>
       <c r="B64" s="28"/>
       <c r="C64" s="32"/>
     </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="155" t="s">
         <v>0</v>
       </c>
@@ -2329,24 +2329,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="232" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="B66" s="233"/>
-      <c r="C66" s="233"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="233"/>
-      <c r="B67" s="233"/>
-      <c r="C67" s="233"/>
-    </row>
-    <row r="68" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="233"/>
-      <c r="B68" s="233"/>
-      <c r="C68" s="233"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B66" s="235"/>
+      <c r="C66" s="235"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="235"/>
+      <c r="B67" s="235"/>
+      <c r="C67" s="235"/>
+    </row>
+    <row r="68" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="235"/>
+      <c r="B68" s="235"/>
+      <c r="C68" s="235"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -2374,56 +2374,56 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="9" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" style="11" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="11" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="222">
+      <c r="B1" s="225">
         <f>N1</f>
         <v>1237643.807</v>
       </c>
-      <c r="C1" s="222"/>
+      <c r="C1" s="225"/>
       <c r="D1" s="138">
         <v>1667839.1270000001</v>
       </c>
       <c r="E1" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="224"/>
-      <c r="H1" s="224"/>
-      <c r="I1" s="225" t="s">
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="228" t="s">
         <v>112</v>
       </c>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="222">
+      <c r="J1" s="228"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="225">
         <v>1000000</v>
       </c>
-      <c r="M1" s="222"/>
+      <c r="M1" s="225"/>
       <c r="N1">
         <v>1237643.807</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>114343.59853770002</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>113896.06977629999</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>140146.98204048874</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="62" t="s">
         <v>37</v>
       </c>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="P6" s="175"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="175"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
         <v>40</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>113896.06977629999</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>42</v>
       </c>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="P9" s="175"/>
     </row>
-    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="177" t="s">
         <v>44</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>113896.06977629999</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>112777.2478728</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
         <v>47</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>116581.2423447</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>49</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>114343.59853770002</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="62" t="s">
         <v>49</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>113858.94467160697</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>53</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>242398.76089648317</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
         <v>56</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>116581.2423447</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>59</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>112777.24787279998</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="204" t="s">
         <v>61</v>
       </c>
@@ -3304,7 +3304,7 @@
       <c r="P18" s="206"/>
       <c r="Q18" s="203"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="62" t="s">
         <v>63</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>165585.641718</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="184"/>
       <c r="B20" s="178" t="s">
         <v>99</v>
@@ -3403,7 +3403,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>57</v>
@@ -3454,7 +3454,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="139"/>
       <c r="B22" s="140"/>
       <c r="C22" s="141" t="s">
@@ -3502,7 +3502,7 @@
         <v>334807.04311161704</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>35</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>49</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
         <v>63</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>63</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>241771.51623107606</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="66"/>
       <c r="B28" s="65" t="str">
         <f>B7</f>
@@ -3817,7 +3817,7 @@
         <v>24166.5531156</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="66" t="s">
         <v>53</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>50780.48926987873</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="68"/>
@@ -3882,7 +3882,7 @@
       <c r="L30" s="71"/>
       <c r="M30" s="71"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="72"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74" t="s">
@@ -3914,72 +3914,72 @@
         <v>3398007.4200824555</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K32" s="22"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="223" t="s">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="226" t="s">
         <v>109</v>
       </c>
-      <c r="B33" s="223"/>
-      <c r="C33" s="223"/>
-      <c r="D33" s="223"/>
-      <c r="E33" s="223"/>
-      <c r="F33" s="223"/>
-      <c r="G33" s="223"/>
-      <c r="H33" s="223"/>
-      <c r="I33" s="223"/>
-      <c r="J33" s="223"/>
-      <c r="K33" s="223"/>
-      <c r="L33" s="223"/>
-      <c r="M33" s="223"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="223"/>
-      <c r="B34" s="223"/>
-      <c r="C34" s="223"/>
-      <c r="D34" s="223"/>
-      <c r="E34" s="223"/>
-      <c r="F34" s="223"/>
-      <c r="G34" s="223"/>
-      <c r="H34" s="223"/>
-      <c r="I34" s="223"/>
-      <c r="J34" s="223"/>
-      <c r="K34" s="223"/>
-      <c r="L34" s="223"/>
-      <c r="M34" s="223"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="223"/>
-      <c r="B35" s="223"/>
-      <c r="C35" s="223"/>
-      <c r="D35" s="223"/>
-      <c r="E35" s="223"/>
-      <c r="F35" s="223"/>
-      <c r="G35" s="223"/>
-      <c r="H35" s="223"/>
-      <c r="I35" s="223"/>
-      <c r="J35" s="223"/>
-      <c r="K35" s="223"/>
-      <c r="L35" s="223"/>
-      <c r="M35" s="223"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="223"/>
-      <c r="B36" s="223"/>
-      <c r="C36" s="223"/>
-      <c r="D36" s="223"/>
-      <c r="E36" s="223"/>
-      <c r="F36" s="223"/>
-      <c r="G36" s="223"/>
-      <c r="H36" s="223"/>
-      <c r="I36" s="223"/>
-      <c r="J36" s="223"/>
-      <c r="K36" s="223"/>
-      <c r="L36" s="223"/>
-      <c r="M36" s="223"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B33" s="226"/>
+      <c r="C33" s="226"/>
+      <c r="D33" s="226"/>
+      <c r="E33" s="226"/>
+      <c r="F33" s="226"/>
+      <c r="G33" s="226"/>
+      <c r="H33" s="226"/>
+      <c r="I33" s="226"/>
+      <c r="J33" s="226"/>
+      <c r="K33" s="226"/>
+      <c r="L33" s="226"/>
+      <c r="M33" s="226"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="226"/>
+      <c r="B34" s="226"/>
+      <c r="C34" s="226"/>
+      <c r="D34" s="226"/>
+      <c r="E34" s="226"/>
+      <c r="F34" s="226"/>
+      <c r="G34" s="226"/>
+      <c r="H34" s="226"/>
+      <c r="I34" s="226"/>
+      <c r="J34" s="226"/>
+      <c r="K34" s="226"/>
+      <c r="L34" s="226"/>
+      <c r="M34" s="226"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="226"/>
+      <c r="B35" s="226"/>
+      <c r="C35" s="226"/>
+      <c r="D35" s="226"/>
+      <c r="E35" s="226"/>
+      <c r="F35" s="226"/>
+      <c r="G35" s="226"/>
+      <c r="H35" s="226"/>
+      <c r="I35" s="226"/>
+      <c r="J35" s="226"/>
+      <c r="K35" s="226"/>
+      <c r="L35" s="226"/>
+      <c r="M35" s="226"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="226"/>
+      <c r="B36" s="226"/>
+      <c r="C36" s="226"/>
+      <c r="D36" s="226"/>
+      <c r="E36" s="226"/>
+      <c r="F36" s="226"/>
+      <c r="G36" s="226"/>
+      <c r="H36" s="226"/>
+      <c r="I36" s="226"/>
+      <c r="J36" s="226"/>
+      <c r="K36" s="226"/>
+      <c r="L36" s="226"/>
+      <c r="M36" s="226"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -3999,45 +3999,45 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="226" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="229" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="227"/>
-      <c r="C1" s="227"/>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
-      <c r="M1" s="227"/>
-      <c r="N1" s="228"/>
+      <c r="B1" s="230"/>
+      <c r="C1" s="230"/>
+      <c r="D1" s="230"/>
+      <c r="E1" s="230"/>
+      <c r="F1" s="230"/>
+      <c r="G1" s="230"/>
+      <c r="H1" s="230"/>
+      <c r="I1" s="230"/>
+      <c r="J1" s="230"/>
+      <c r="K1" s="230"/>
+      <c r="L1" s="230"/>
+      <c r="M1" s="230"/>
+      <c r="N1" s="231"/>
       <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
       <c r="C2" s="161"/>
@@ -4055,7 +4055,7 @@
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
       <c r="C3" s="163"/>
@@ -4073,7 +4073,7 @@
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
       <c r="C4" s="163"/>
@@ -4093,7 +4093,7 @@
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
       <c r="C5" s="163"/>
@@ -4111,7 +4111,7 @@
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
       <c r="C6" s="209" t="str">
@@ -4132,7 +4132,7 @@
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81"/>
       <c r="B7" s="81" t="s">
         <v>77</v>
@@ -4159,7 +4159,7 @@
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81"/>
       <c r="B8" s="80" t="s">
         <v>77</v>
@@ -4175,16 +4175,16 @@
         <f>C8-J38</f>
         <v>-306814.79180000001</v>
       </c>
-      <c r="L8" s="230">
+      <c r="L8" s="233">
         <f>C7-J38</f>
         <v>359706.75820000004</v>
       </c>
-      <c r="M8" s="230"/>
+      <c r="M8" s="233"/>
       <c r="N8" s="84"/>
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="87" t="s">
         <v>78</v>
       </c>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="98">
         <v>1</v>
       </c>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="99">
         <v>2</v>
       </c>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="98">
         <v>3</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="98">
         <v>4</v>
       </c>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="98">
         <v>6</v>
       </c>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="98">
         <v>7</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>193262.33236106002</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="98">
         <v>8</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>176418.02467122104</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="98">
         <v>9</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>156160.19516105996</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="98">
         <v>10</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>173495.33869936003</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="98">
         <v>11</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>217631.51514914012</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="98">
         <v>12</v>
       </c>
@@ -4842,7 +4842,7 @@
         <v>210060.13742574007</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="98">
         <v>13</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>164132.47985636702</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="98">
         <v>14</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>316415.8483230432</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="98">
         <v>15</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>202062.87314913995</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="98">
         <v>16</v>
       </c>
@@ -5062,7 +5062,7 @@
         <v>157439.00429935998</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="98">
         <v>17</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>169068.60654914001</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="98">
         <v>18</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>284810.77513159986</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="98">
         <v>19</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="98">
         <v>20</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="98"/>
       <c r="B29" s="90"/>
       <c r="C29" s="158" t="s">
@@ -5286,7 +5286,7 @@
         <v>342576.70908873709</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="98"/>
       <c r="B30" s="90"/>
       <c r="C30" s="169" t="s">
@@ -5318,7 +5318,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="98"/>
       <c r="B31" s="90"/>
       <c r="C31" s="169" t="s">
@@ -5352,7 +5352,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="99"/>
       <c r="B32" s="208"/>
       <c r="C32" s="169" t="s">
@@ -5386,7 +5386,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="98"/>
       <c r="B33" s="90"/>
       <c r="C33" s="130" t="s">
@@ -5420,7 +5420,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="98"/>
       <c r="B34" s="90"/>
       <c r="C34" s="130" t="s">
@@ -5454,7 +5454,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="98">
         <v>21</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>31936.219092719999</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="98">
         <v>22</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>58550.155246998736</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="98">
         <v>23</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="98">
         <v>24</v>
       </c>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78"/>
       <c r="C39" s="91"/>
       <c r="D39" s="92"/>
@@ -5617,41 +5617,41 @@
       <c r="N39" s="93"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="229"/>
-      <c r="D40" s="227"/>
-      <c r="E40" s="227"/>
-      <c r="F40" s="227"/>
-      <c r="G40" s="227"/>
-      <c r="H40" s="227"/>
-      <c r="I40" s="227"/>
-      <c r="J40" s="227"/>
-      <c r="K40" s="227"/>
-      <c r="L40" s="227"/>
-      <c r="M40" s="227"/>
-      <c r="N40" s="227"/>
+      <c r="C40" s="232"/>
+      <c r="D40" s="230"/>
+      <c r="E40" s="230"/>
+      <c r="F40" s="230"/>
+      <c r="G40" s="230"/>
+      <c r="H40" s="230"/>
+      <c r="I40" s="230"/>
+      <c r="J40" s="230"/>
+      <c r="K40" s="230"/>
+      <c r="L40" s="230"/>
+      <c r="M40" s="230"/>
+      <c r="N40" s="230"/>
       <c r="O40" s="95"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H41" s="79"/>
       <c r="J41" s="96"/>
       <c r="K41" s="96"/>
       <c r="L41" s="96"/>
       <c r="N41" s="97"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L44" s="151"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="96"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E46" s="152"/>
       <c r="F46" s="152"/>
       <c r="G46" s="152"/>
